--- a/事業計画_Ver1.5.xlsx
+++ b/事業計画_Ver1.5.xlsx
@@ -4785,11 +4785,11 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>② ツール ÷ Synthesia</t>
+          <t>② ツール（ARRベース）÷ Synthesia</t>
         </is>
       </c>
       <c r="B17" s="10">
-        <f>'損益計算書'!$G$10/100/210</f>
+        <f>'商品マスタ②'!$G$45/100/210</f>
         <v/>
       </c>
     </row>
@@ -8800,7 +8800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8845,7 +8845,11 @@
           <t>単価(万円)</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>継続/一過性</t>
+        </is>
+      </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
@@ -8871,6 +8875,11 @@
       <c r="C4" s="18" t="n">
         <v>300</v>
       </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>継続</t>
+        </is>
+      </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
           <t>全業種・商用利用</t>
@@ -8891,6 +8900,11 @@
       <c r="C5" s="18" t="n">
         <v>100</v>
       </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>継続</t>
+        </is>
+      </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
           <t>1業種</t>
@@ -8911,6 +8925,11 @@
       <c r="C6" s="18" t="n">
         <v>24</v>
       </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>継続</t>
+        </is>
+      </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
           <t>1席あたり年額</t>
@@ -8931,6 +8950,11 @@
       <c r="C7" s="18" t="n">
         <v>24</v>
       </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>継続</t>
+        </is>
+      </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
           <t>追加学習モデルの更新・再学習</t>
@@ -8951,9 +8975,14 @@
       <c r="C8" s="18" t="n">
         <v>80</v>
       </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>一過性</t>
+        </is>
+      </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>顧客のブランド・商品を学習</t>
+          <t>毎年は発生しない。ARRには入らない</t>
         </is>
       </c>
     </row>
@@ -9638,8 +9667,204 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>ARRベース（継続課金のみ）— Synthesia・HeyGenと同じ土俵で比べるための行</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr"/>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>1期</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>2期</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>3期</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>4期</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>5期</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr"/>
+      <c r="I42" s="3" t="inlineStr"/>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>考え方</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>法人ARR / 社（万円）</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr"/>
+      <c r="C43" s="23">
+        <f>IF(C19=0,0,C23-$C$15)</f>
+        <v/>
+      </c>
+      <c r="D43" s="23">
+        <f>IF(D19=0,0,D23-$C$15)</f>
+        <v/>
+      </c>
+      <c r="E43" s="23">
+        <f>IF(E19=0,0,E23-$C$15)</f>
+        <v/>
+      </c>
+      <c r="F43" s="23">
+        <f>IF(F19=0,0,F23-$C$15)</f>
+        <v/>
+      </c>
+      <c r="G43" s="23">
+        <f>IF(G19=0,0,G23-$C$15)</f>
+        <v/>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>積み上げACVから LoRA個別構築の20万を除く</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>法人ARR（百万円）</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr"/>
+      <c r="C44" s="23">
+        <f>C19*C43/100</f>
+        <v/>
+      </c>
+      <c r="D44" s="23">
+        <f>D19*D43/100</f>
+        <v/>
+      </c>
+      <c r="E44" s="23">
+        <f>E19*E43/100</f>
+        <v/>
+      </c>
+      <c r="F44" s="23">
+        <f>F19*F43/100</f>
+        <v/>
+      </c>
+      <c r="G44" s="23">
+        <f>G19*G43/100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>② ARR 合計（百万円）</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr"/>
+      <c r="C45" s="6">
+        <f>C44+C27+C35*$B$47</f>
+        <v/>
+      </c>
+      <c r="D45" s="6">
+        <f>D44+D27+D35*$B$47</f>
+        <v/>
+      </c>
+      <c r="E45" s="6">
+        <f>E44+E27+E35*$B$47</f>
+        <v/>
+      </c>
+      <c r="F45" s="6">
+        <f>F44+F27+F35*$B$47</f>
+        <v/>
+      </c>
+      <c r="G45" s="6">
+        <f>G44+G27+G35*$B$47</f>
+        <v/>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>法人ARR ＋ 個人 ＋ セルフサーブの継続分</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>一過性収入（百万円）</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr"/>
+      <c r="C46" s="23">
+        <f>C38-C45</f>
+        <v/>
+      </c>
+      <c r="D46" s="23">
+        <f>D38-D45</f>
+        <v/>
+      </c>
+      <c r="E46" s="23">
+        <f>E38-E45</f>
+        <v/>
+      </c>
+      <c r="F46" s="23">
+        <f>F38-F45</f>
+        <v/>
+      </c>
+      <c r="G46" s="23">
+        <f>G38-G45</f>
+        <v/>
+      </c>
+      <c r="J46" s="7" t="inlineStr">
+        <is>
+          <t>LoRA個別構築とセルフサーブの都度課金</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>②-C のうち継続課金の比率</t>
+        </is>
+      </c>
+      <c r="B47" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>★月額980円と都度1,500円/本の混合。都度分はARRに入らない</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>② 売上（ACVベース）と ② ARR の差が一過性収入。投資家に「御社のARRは？」と聞かれたら下の行を答える。デッキで Synthesia 210億・HeyGen 300億と並べているが、あちらの公表値はARRなので揃える必要がある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>②-C はここに置く（③ではなく）。ツール事業の倍率が当たる側で、会社の形も3事業のまま保てる。</t>
         </is>

--- a/事業計画_Ver1.5.xlsx
+++ b/事業計画_Ver1.5.xlsx
@@ -625,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1164,227 +1164,444 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>シード投資家（1.42億）のリターン</t>
+          <t>継続収益（ARR）と非継続の内訳</t>
         </is>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>ケース</t>
+          <t>項目</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr"/>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>時価総額(億)</t>
+          <t>1期</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>取り分(億)</t>
+          <t>2期</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>倍率</t>
+          <t>3期</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>IRR</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr"/>
+          <t>4期</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>5期</t>
+        </is>
+      </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>根拠</t>
+          <t>考え方</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>ライン別・保守</t>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>① 映像制作 ARR</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="8">
-        <f>'資本政策とリターン'!E13</f>
-        <v/>
-      </c>
-      <c r="D22" s="13">
-        <f>'資本政策とリターン'!F13</f>
-        <v/>
-      </c>
-      <c r="E22" s="14">
-        <f>'資本政策とリターン'!G13</f>
-        <v/>
-      </c>
-      <c r="F22" s="10">
-        <f>'資本政策とリターン'!H13</f>
-        <v/>
-      </c>
-      <c r="G22" s="5" t="inlineStr"/>
+        <f>'商品マスタ①'!I21</f>
+        <v/>
+      </c>
+      <c r="D22" s="8">
+        <f>'商品マスタ①'!J21</f>
+        <v/>
+      </c>
+      <c r="E22" s="8">
+        <f>'商品マスタ①'!K21</f>
+        <v/>
+      </c>
+      <c r="F22" s="8">
+        <f>'商品マスタ①'!L21</f>
+        <v/>
+      </c>
+      <c r="G22" s="8">
+        <f>'商品マスタ①'!M21</f>
+        <v/>
+      </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>ツール6倍＋C2C4倍＋制作1.5倍</t>
+          <t>案件ベース。リテイナー契約分のみ（いまは0）</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>ライン別・中庸</t>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>② ツール外販 ARR</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr"/>
       <c r="C23" s="8">
-        <f>'資本政策とリターン'!E14</f>
-        <v/>
-      </c>
-      <c r="D23" s="13">
-        <f>'資本政策とリターン'!F14</f>
-        <v/>
-      </c>
-      <c r="E23" s="14">
-        <f>'資本政策とリターン'!G14</f>
-        <v/>
-      </c>
-      <c r="F23" s="10">
-        <f>'資本政策とリターン'!H14</f>
-        <v/>
-      </c>
-      <c r="G23" s="5" t="inlineStr"/>
+        <f>'商品マスタ②'!C45</f>
+        <v/>
+      </c>
+      <c r="D23" s="8">
+        <f>'商品マスタ②'!D45</f>
+        <v/>
+      </c>
+      <c r="E23" s="8">
+        <f>'商品マスタ②'!E45</f>
+        <v/>
+      </c>
+      <c r="F23" s="8">
+        <f>'商品マスタ②'!F45</f>
+        <v/>
+      </c>
+      <c r="G23" s="8">
+        <f>'商品マスタ②'!G45</f>
+        <v/>
+      </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>ツール7倍＋C2C5倍＋制作2.0倍</t>
+          <t>LoRA個別構築とセルフサーブ都度分を除く</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>ライン別・強気</t>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>③ 越境C2C ARR</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr"/>
       <c r="C24" s="8">
-        <f>'資本政策とリターン'!E15</f>
-        <v/>
-      </c>
-      <c r="D24" s="13">
-        <f>'資本政策とリターン'!F15</f>
-        <v/>
-      </c>
-      <c r="E24" s="14">
-        <f>'資本政策とリターン'!G15</f>
-        <v/>
-      </c>
-      <c r="F24" s="10">
-        <f>'資本政策とリターン'!H15</f>
-        <v/>
-      </c>
-      <c r="G24" s="5" t="inlineStr"/>
+        <f>'商品マスタ③'!C49</f>
+        <v/>
+      </c>
+      <c r="D24" s="8">
+        <f>'商品マスタ③'!D49</f>
+        <v/>
+      </c>
+      <c r="E24" s="8">
+        <f>'商品マスタ③'!E49</f>
+        <v/>
+      </c>
+      <c r="F24" s="8">
+        <f>'商品マスタ③'!F49</f>
+        <v/>
+      </c>
+      <c r="G24" s="8">
+        <f>'商品マスタ③'!G49</f>
+        <v/>
+      </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>ツール8倍＋C2C6倍＋制作2.5倍</t>
+          <t>取引ベースなのでゼロ</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>全社 PSR 4倍</t>
+          <t>全社 ARR</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr"/>
-      <c r="C25" s="8">
-        <f>'資本政策とリターン'!E19</f>
-        <v/>
-      </c>
-      <c r="D25" s="13">
-        <f>'資本政策とリターン'!F19</f>
-        <v/>
-      </c>
-      <c r="E25" s="14">
-        <f>'資本政策とリターン'!G19</f>
-        <v/>
-      </c>
-      <c r="F25" s="10">
-        <f>'資本政策とリターン'!H19</f>
-        <v/>
-      </c>
-      <c r="G25" s="5" t="inlineStr"/>
+      <c r="C25" s="6">
+        <f>C22+C23+C24</f>
+        <v/>
+      </c>
+      <c r="D25" s="6">
+        <f>D22+D23+D24</f>
+        <v/>
+      </c>
+      <c r="E25" s="6">
+        <f>E22+E23+E24</f>
+        <v/>
+      </c>
+      <c r="F25" s="6">
+        <f>F22+F23+F24</f>
+        <v/>
+      </c>
+      <c r="G25" s="6">
+        <f>G22+G23+G24</f>
+        <v/>
+      </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>人手に比例しない収益が9割であること</t>
+          <t>投資家に「御社のARRは？」と聞かれたらこの行</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">　ARR比率（対 売上）</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="9">
+        <f>IF(C4=0,0,C25/C4)</f>
+        <v/>
+      </c>
+      <c r="D26" s="9">
+        <f>IF(D4=0,0,D25/D4)</f>
+        <v/>
+      </c>
+      <c r="E26" s="9">
+        <f>IF(E4=0,0,E25/E4)</f>
+        <v/>
+      </c>
+      <c r="F26" s="9">
+        <f>IF(F4=0,0,F25/F4)</f>
+        <v/>
+      </c>
+      <c r="G26" s="9">
+        <f>IF(G4=0,0,G25/G4)</f>
+        <v/>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>②以外は継続収益にならない</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>⚠ 継続収益になるのは②だけ。①は案件ベース、③は取引ベース。下のライン別評価でツール6〜8倍・C2C4〜6倍・制作1.5〜2.5倍と差をつけているのは、まさにこの違いを反映している。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>シード投資家（1.42億）のリターン</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>ケース</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>時価総額(億)</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>取り分(億)</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>倍率</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>IRR</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ライン別・保守</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="8">
+        <f>'資本政策とリターン'!E13</f>
+        <v/>
+      </c>
+      <c r="D31" s="13">
+        <f>'資本政策とリターン'!F13</f>
+        <v/>
+      </c>
+      <c r="E31" s="14">
+        <f>'資本政策とリターン'!G13</f>
+        <v/>
+      </c>
+      <c r="F31" s="10">
+        <f>'資本政策とリターン'!H13</f>
+        <v/>
+      </c>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>ツール6倍＋C2C4倍＋制作1.5倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ライン別・中庸</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="8">
+        <f>'資本政策とリターン'!E14</f>
+        <v/>
+      </c>
+      <c r="D32" s="13">
+        <f>'資本政策とリターン'!F14</f>
+        <v/>
+      </c>
+      <c r="E32" s="14">
+        <f>'資本政策とリターン'!G14</f>
+        <v/>
+      </c>
+      <c r="F32" s="10">
+        <f>'資本政策とリターン'!H14</f>
+        <v/>
+      </c>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>ツール7倍＋C2C5倍＋制作2.0倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>ライン別・強気</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="8">
+        <f>'資本政策とリターン'!E15</f>
+        <v/>
+      </c>
+      <c r="D33" s="13">
+        <f>'資本政策とリターン'!F15</f>
+        <v/>
+      </c>
+      <c r="E33" s="14">
+        <f>'資本政策とリターン'!G15</f>
+        <v/>
+      </c>
+      <c r="F33" s="10">
+        <f>'資本政策とリターン'!H15</f>
+        <v/>
+      </c>
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>ツール8倍＋C2C6倍＋制作2.5倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>全社 PSR 4倍</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr"/>
+      <c r="C34" s="8">
+        <f>'資本政策とリターン'!E19</f>
+        <v/>
+      </c>
+      <c r="D34" s="13">
+        <f>'資本政策とリターン'!F19</f>
+        <v/>
+      </c>
+      <c r="E34" s="14">
+        <f>'資本政策とリターン'!G19</f>
+        <v/>
+      </c>
+      <c r="F34" s="10">
+        <f>'資本政策とリターン'!H19</f>
+        <v/>
+      </c>
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>人手に比例しない収益が9割であること</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
           <t>全社 PSR 5倍</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr"/>
-      <c r="C26" s="8">
+      <c r="B35" s="5" t="inlineStr"/>
+      <c r="C35" s="8">
         <f>'資本政策とリターン'!E20</f>
         <v/>
       </c>
-      <c r="D26" s="13">
+      <c r="D35" s="13">
         <f>'資本政策とリターン'!F20</f>
         <v/>
       </c>
-      <c r="E26" s="14">
+      <c r="E35" s="14">
         <f>'資本政策とリターン'!G20</f>
         <v/>
       </c>
-      <c r="F26" s="10">
+      <c r="F35" s="10">
         <f>'資本政策とリターン'!H20</f>
         <v/>
       </c>
-      <c r="G26" s="5" t="inlineStr"/>
-      <c r="H26" s="7" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>⚠ 上の倍率は事業計画からの逆算であって、投資の推奨でも利回りの保証でもない。前提の多くは未実証（「出所と仮置き」シート参照）。</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
         <is>
           <t>このモデルの読み方</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>入力は「前提」と3つの「商品マスタ」の黄色セルだけ。ほかは全部そこを参照する数式。</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>①の平均単価と平均難度は、商品構成比から導出される。直接は入力できない。</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>③は成約が価格帯のどこに落ちるかで3倍動く。いまは中点（均等）を採用している。</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>⚠ xlsx を手で編集しないこと。make_xlsx15.py を直して再生成する。</t>
         </is>
@@ -7689,7 +7906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -8217,6 +8434,207 @@
       <c r="M15" s="23">
         <f>M12*M10*'前提'!$G$5/100</f>
         <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>ACV / ARR — ①は案件ベースなので、そのままではARRにならない</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>1期</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>2期</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>3期</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>4期</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>5期</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>考え方</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>取引アカウント数</t>
+        </is>
+      </c>
+      <c r="I19" s="23">
+        <f>'営業体制'!C22</f>
+        <v/>
+      </c>
+      <c r="J19" s="23">
+        <f>'営業体制'!D22</f>
+        <v/>
+      </c>
+      <c r="K19" s="23">
+        <f>'営業体制'!E22</f>
+        <v/>
+      </c>
+      <c r="L19" s="23">
+        <f>'営業体制'!F22</f>
+        <v/>
+      </c>
+      <c r="M19" s="23">
+        <f>'営業体制'!G22</f>
+        <v/>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>営業体制シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>アカウントあたり年間取引額（万円）</t>
+        </is>
+      </c>
+      <c r="I20" s="23">
+        <f>IF(I19=0,0,I13*100/I19)</f>
+        <v/>
+      </c>
+      <c r="J20" s="23">
+        <f>IF(J19=0,0,J13*100/J19)</f>
+        <v/>
+      </c>
+      <c r="K20" s="23">
+        <f>IF(K19=0,0,K13*100/K19)</f>
+        <v/>
+      </c>
+      <c r="L20" s="23">
+        <f>IF(L19=0,0,L13*100/L19)</f>
+        <v/>
+      </c>
+      <c r="M20" s="23">
+        <f>IF(M19=0,0,M13*100/M19)</f>
+        <v/>
+      </c>
+      <c r="N20" s="7" t="inlineStr">
+        <is>
+          <t>ACV相当。ただし契約ではなく案件の集まり</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>① ARR（百万円）</t>
+        </is>
+      </c>
+      <c r="I21" s="6">
+        <f>I13*$B$22</f>
+        <v/>
+      </c>
+      <c r="J21" s="6">
+        <f>J13*$B$22</f>
+        <v/>
+      </c>
+      <c r="K21" s="6">
+        <f>K13*$B$22</f>
+        <v/>
+      </c>
+      <c r="L21" s="6">
+        <f>L13*$B$22</f>
+        <v/>
+      </c>
+      <c r="M21" s="6">
+        <f>M13*$B$22</f>
+        <v/>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>リテイナー契約分のみ。スポット受注はARRではない</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>年間リテイナー契約の比率</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="7" t="inlineStr">
+        <is>
+          <t>★「年◯本でいくら」の包括契約にした分だけARRに入る。いまは0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>① 非継続（百万円）</t>
+        </is>
+      </c>
+      <c r="I23" s="23">
+        <f>I13-I21</f>
+        <v/>
+      </c>
+      <c r="J23" s="23">
+        <f>J13-J21</f>
+        <v/>
+      </c>
+      <c r="K23" s="23">
+        <f>K13-K21</f>
+        <v/>
+      </c>
+      <c r="L23" s="23">
+        <f>L13-L21</f>
+        <v/>
+      </c>
+      <c r="M23" s="23">
+        <f>M13-M21</f>
+        <v/>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>案件ごとの発注。毎年の継続は保証されない</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>①は1本ごとの発注で、翌年も同じ社が同じ本数を出す義務はない。だから「1社あたり年567万」はACV相当ではあってもARRではない。年間包括（リテイナー）契約を商品として作れば、その分はARRに算入できる。★要判断</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -9881,7 +10299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -11128,6 +11546,126 @@
       <c r="A45" s="36" t="inlineStr">
         <is>
           <t>成約が価格帯のどこに落ちるかで③は3倍動く。ここは中点（均等）を採用している（松田さん決定）。下限寄りに寄ると小さくなる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>ACV / ARR — ③は取引ベースなのでARRはゼロ</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr"/>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>1期</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>2期</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>3期</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>4期</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>5期</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr"/>
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>考え方</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>③ ARR（百万円）</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr"/>
+      <c r="C49" s="23">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D49" s="23">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E49" s="23">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F49" s="23">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G49" s="23">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>取引手数料。契約ではないのでARRに算入できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>③ 非継続（百万円）</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr"/>
+      <c r="C50" s="23">
+        <f>C41</f>
+        <v/>
+      </c>
+      <c r="D50" s="23">
+        <f>D41</f>
+        <v/>
+      </c>
+      <c r="E50" s="23">
+        <f>E41</f>
+        <v/>
+      </c>
+      <c r="F50" s="23">
+        <f>F41</f>
+        <v/>
+      </c>
+      <c r="G50" s="23">
+        <f>G41</f>
+        <v/>
+      </c>
+      <c r="K50" s="7" t="inlineStr">
+        <is>
+          <t>全額が取引ベース</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>マーケットプレイスはARRでは評価されない。見るのは GMV・取引件数・手数料率・そして発注者のリピート率。リピート率はまだモデルに入っていない。★次に詰めるならここ</t>
         </is>
       </c>
     </row>

--- a/事業計画_Ver1.5.xlsx
+++ b/事業計画_Ver1.5.xlsx
@@ -855,23 +855,23 @@
       </c>
       <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="6">
-        <f>'損益計算書'!C28</f>
+        <f>'損益計算書'!C29</f>
         <v/>
       </c>
       <c r="D9" s="6">
-        <f>'損益計算書'!D28</f>
+        <f>'損益計算書'!D29</f>
         <v/>
       </c>
       <c r="E9" s="6">
-        <f>'損益計算書'!E28</f>
+        <f>'損益計算書'!E29</f>
         <v/>
       </c>
       <c r="F9" s="6">
-        <f>'損益計算書'!F28</f>
+        <f>'損益計算書'!F29</f>
         <v/>
       </c>
       <c r="G9" s="6">
-        <f>'損益計算書'!G28</f>
+        <f>'損益計算書'!G29</f>
         <v/>
       </c>
       <c r="H9" s="7" t="inlineStr"/>
@@ -884,23 +884,23 @@
       </c>
       <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="9">
-        <f>'損益計算書'!C29</f>
+        <f>'損益計算書'!C30</f>
         <v/>
       </c>
       <c r="D10" s="9">
-        <f>'損益計算書'!D29</f>
+        <f>'損益計算書'!D30</f>
         <v/>
       </c>
       <c r="E10" s="9">
-        <f>'損益計算書'!E29</f>
+        <f>'損益計算書'!E30</f>
         <v/>
       </c>
       <c r="F10" s="9">
-        <f>'損益計算書'!F29</f>
+        <f>'損益計算書'!F30</f>
         <v/>
       </c>
       <c r="G10" s="9">
-        <f>'損益計算書'!G29</f>
+        <f>'損益計算書'!G30</f>
         <v/>
       </c>
       <c r="H10" s="7" t="inlineStr"/>
@@ -979,23 +979,23 @@
       </c>
       <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="8">
-        <f>'損益計算書'!C32</f>
+        <f>'損益計算書'!C33</f>
         <v/>
       </c>
       <c r="D13" s="8">
-        <f>'損益計算書'!D32</f>
+        <f>'損益計算書'!D33</f>
         <v/>
       </c>
       <c r="E13" s="8">
-        <f>'損益計算書'!E32</f>
+        <f>'損益計算書'!E33</f>
         <v/>
       </c>
       <c r="F13" s="8">
-        <f>'損益計算書'!F32</f>
+        <f>'損益計算書'!F33</f>
         <v/>
       </c>
       <c r="G13" s="8">
-        <f>'損益計算書'!G32</f>
+        <f>'損益計算書'!G33</f>
         <v/>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -1012,23 +1012,23 @@
       </c>
       <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="6">
-        <f>'損益計算書'!C33</f>
+        <f>'損益計算書'!C34</f>
         <v/>
       </c>
       <c r="D14" s="6">
-        <f>'損益計算書'!D33</f>
+        <f>'損益計算書'!D34</f>
         <v/>
       </c>
       <c r="E14" s="6">
-        <f>'損益計算書'!E33</f>
+        <f>'損益計算書'!E34</f>
         <v/>
       </c>
       <c r="F14" s="6">
-        <f>'損益計算書'!F33</f>
+        <f>'損益計算書'!F34</f>
         <v/>
       </c>
       <c r="G14" s="6">
-        <f>'損益計算書'!G33</f>
+        <f>'損益計算書'!G34</f>
         <v/>
       </c>
       <c r="H14" s="7" t="inlineStr"/>
@@ -1041,23 +1041,23 @@
       </c>
       <c r="B15" s="5" t="inlineStr"/>
       <c r="C15" s="9">
-        <f>'損益計算書'!C36</f>
+        <f>'損益計算書'!C37</f>
         <v/>
       </c>
       <c r="D15" s="9">
-        <f>'損益計算書'!D36</f>
+        <f>'損益計算書'!D37</f>
         <v/>
       </c>
       <c r="E15" s="9">
-        <f>'損益計算書'!E36</f>
+        <f>'損益計算書'!E37</f>
         <v/>
       </c>
       <c r="F15" s="9">
-        <f>'損益計算書'!F36</f>
+        <f>'損益計算書'!F37</f>
         <v/>
       </c>
       <c r="G15" s="9">
-        <f>'損益計算書'!G36</f>
+        <f>'損益計算書'!G37</f>
         <v/>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -1074,23 +1074,23 @@
       </c>
       <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="10">
-        <f>'損益計算書'!C34</f>
+        <f>'損益計算書'!C35</f>
         <v/>
       </c>
       <c r="D16" s="10">
-        <f>'損益計算書'!D34</f>
+        <f>'損益計算書'!D35</f>
         <v/>
       </c>
       <c r="E16" s="10">
-        <f>'損益計算書'!E34</f>
+        <f>'損益計算書'!E35</f>
         <v/>
       </c>
       <c r="F16" s="10">
-        <f>'損益計算書'!F34</f>
+        <f>'損益計算書'!F35</f>
         <v/>
       </c>
       <c r="G16" s="10">
-        <f>'損益計算書'!G34</f>
+        <f>'損益計算書'!G35</f>
         <v/>
       </c>
       <c r="H16" s="7" t="inlineStr"/>
@@ -1136,23 +1136,23 @@
       </c>
       <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="8">
-        <f>'損益計算書'!C37</f>
+        <f>'損益計算書'!C38</f>
         <v/>
       </c>
       <c r="D18" s="8">
-        <f>'損益計算書'!D37</f>
+        <f>'損益計算書'!D38</f>
         <v/>
       </c>
       <c r="E18" s="8">
-        <f>'損益計算書'!E37</f>
+        <f>'損益計算書'!E38</f>
         <v/>
       </c>
       <c r="F18" s="8">
-        <f>'損益計算書'!F37</f>
+        <f>'損益計算書'!F38</f>
         <v/>
       </c>
       <c r="G18" s="8">
-        <f>'損益計算書'!G37</f>
+        <f>'損益計算書'!G38</f>
         <v/>
       </c>
       <c r="H18" s="7" t="inlineStr">
@@ -1618,7 +1618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2159,427 +2159,460 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>研究開発費</t>
+          <t>開発委託費（オフショア）</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="8">
-        <f>'前提'!$C$9</f>
+        <f>'人員と人件費'!C34</f>
         <v/>
       </c>
       <c r="D22" s="8">
-        <f>'前提'!$D$9</f>
+        <f>'人員と人件費'!D34</f>
         <v/>
       </c>
       <c r="E22" s="8">
-        <f>'前提'!$E$9</f>
+        <f>'人員と人件費'!E34</f>
         <v/>
       </c>
       <c r="F22" s="8">
-        <f>'前提'!$F$9</f>
+        <f>'人員と人件費'!F34</f>
         <v/>
       </c>
       <c r="G22" s="8">
-        <f>'前提'!$G$9</f>
+        <f>'人員と人件費'!G34</f>
         <v/>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>AX倍率を上げ続けるための投資</t>
+          <t>中国・ベトナム・東欧。PM1名あたり5名</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>BPO（CS・運用）</t>
+          <t>研究開発費（GPU・基盤）</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr"/>
       <c r="C23" s="8">
-        <f>'前提'!$C$10</f>
+        <f>'前提'!$C$9</f>
         <v/>
       </c>
       <c r="D23" s="8">
-        <f>'前提'!$D$10</f>
+        <f>'前提'!$D$9</f>
         <v/>
       </c>
       <c r="E23" s="8">
-        <f>'前提'!$E$10</f>
+        <f>'前提'!$E$9</f>
         <v/>
       </c>
       <c r="F23" s="8">
-        <f>'前提'!$F$10</f>
+        <f>'前提'!$F$9</f>
         <v/>
       </c>
       <c r="G23" s="8">
-        <f>'前提'!$G$10</f>
-        <v/>
+        <f>'前提'!$G$9</f>
+        <v/>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>クラウドGPU・ライセンス・データ基盤</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>獲得費</t>
+          <t>BPO（CS・運用）</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr"/>
       <c r="C24" s="8">
-        <f>C4*'前提'!$C$12+C10*'前提'!$C$13+'前提'!$C$11</f>
+        <f>'前提'!$C$10</f>
         <v/>
       </c>
       <c r="D24" s="8">
-        <f>D4*'前提'!$D$12+D10*'前提'!$D$13+'前提'!$D$11</f>
+        <f>'前提'!$D$10</f>
         <v/>
       </c>
       <c r="E24" s="8">
-        <f>E4*'前提'!$E$12+E10*'前提'!$E$13+'前提'!$E$11</f>
+        <f>'前提'!$E$10</f>
         <v/>
       </c>
       <c r="F24" s="8">
-        <f>F4*'前提'!$F$12+F10*'前提'!$F$13+'前提'!$F$11</f>
+        <f>'前提'!$F$10</f>
         <v/>
       </c>
       <c r="G24" s="8">
-        <f>G4*'前提'!$G$12+G10*'前提'!$G$13+'前提'!$G$11</f>
+        <f>'前提'!$G$10</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>代理店手数料</t>
+          <t>獲得費</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr"/>
       <c r="C25" s="8">
-        <f>C4*'前提'!$C$14*'前提'!$C$15</f>
+        <f>C4*'前提'!$C$12+C10*'前提'!$C$13+'前提'!$C$11</f>
         <v/>
       </c>
       <c r="D25" s="8">
-        <f>D4*'前提'!$D$14*'前提'!$D$15</f>
+        <f>D4*'前提'!$D$12+D10*'前提'!$D$13+'前提'!$D$11</f>
         <v/>
       </c>
       <c r="E25" s="8">
-        <f>E4*'前提'!$E$14*'前提'!$E$15</f>
+        <f>E4*'前提'!$E$12+E10*'前提'!$E$13+'前提'!$E$11</f>
         <v/>
       </c>
       <c r="F25" s="8">
-        <f>F4*'前提'!$F$14*'前提'!$F$15</f>
+        <f>F4*'前提'!$F$12+F10*'前提'!$F$13+'前提'!$F$11</f>
         <v/>
       </c>
       <c r="G25" s="8">
-        <f>G4*'前提'!$G$14*'前提'!$G$15</f>
-        <v/>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>①の代理店チャネル分のみ</t>
-        </is>
+        <f>G4*'前提'!$G$12+G10*'前提'!$G$13+'前提'!$G$11</f>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>その他販管費</t>
+          <t>代理店手数料</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr"/>
       <c r="C26" s="8">
+        <f>C4*'前提'!$C$14*'前提'!$C$15</f>
+        <v/>
+      </c>
+      <c r="D26" s="8">
+        <f>D4*'前提'!$D$14*'前提'!$D$15</f>
+        <v/>
+      </c>
+      <c r="E26" s="8">
+        <f>E4*'前提'!$E$14*'前提'!$E$15</f>
+        <v/>
+      </c>
+      <c r="F26" s="8">
+        <f>F4*'前提'!$F$14*'前提'!$F$15</f>
+        <v/>
+      </c>
+      <c r="G26" s="8">
+        <f>G4*'前提'!$G$14*'前提'!$G$15</f>
+        <v/>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>①の代理店チャネル分のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>その他販管費</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="8">
         <f>C12*'前提'!$C$16</f>
         <v/>
       </c>
-      <c r="D26" s="8">
+      <c r="D27" s="8">
         <f>D12*'前提'!$D$16</f>
         <v/>
       </c>
-      <c r="E26" s="8">
+      <c r="E27" s="8">
         <f>E12*'前提'!$E$16</f>
         <v/>
       </c>
-      <c r="F26" s="8">
+      <c r="F27" s="8">
         <f>F12*'前提'!$F$16</f>
         <v/>
       </c>
-      <c r="G26" s="8">
+      <c r="G27" s="8">
         <f>G12*'前提'!$G$16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>販売費・一般管理費 計</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr"/>
-      <c r="C27" s="37">
-        <f>SUM(C21:C26)</f>
-        <v/>
-      </c>
-      <c r="D27" s="37">
-        <f>SUM(D21:D26)</f>
-        <v/>
-      </c>
-      <c r="E27" s="37">
-        <f>SUM(E21:E26)</f>
-        <v/>
-      </c>
-      <c r="F27" s="37">
-        <f>SUM(F21:F26)</f>
-        <v/>
-      </c>
-      <c r="G27" s="37">
-        <f>SUM(G21:G26)</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>営業利益</t>
+          <t>販売費・一般管理費 計</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr"/>
-      <c r="C28" s="6">
-        <f>C18-C27</f>
-        <v/>
-      </c>
-      <c r="D28" s="6">
-        <f>D18-D27</f>
-        <v/>
-      </c>
-      <c r="E28" s="6">
-        <f>E18-E27</f>
-        <v/>
-      </c>
-      <c r="F28" s="6">
-        <f>F18-F27</f>
-        <v/>
-      </c>
-      <c r="G28" s="6">
-        <f>G18-G27</f>
+      <c r="C28" s="37">
+        <f>SUM(C21:C27)</f>
+        <v/>
+      </c>
+      <c r="D28" s="37">
+        <f>SUM(D21:D27)</f>
+        <v/>
+      </c>
+      <c r="E28" s="37">
+        <f>SUM(E21:E27)</f>
+        <v/>
+      </c>
+      <c r="F28" s="37">
+        <f>SUM(F21:F27)</f>
+        <v/>
+      </c>
+      <c r="G28" s="37">
+        <f>SUM(G21:G27)</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
+          <t>営業利益</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="6">
+        <f>C18-C28</f>
+        <v/>
+      </c>
+      <c r="D29" s="6">
+        <f>D18-D28</f>
+        <v/>
+      </c>
+      <c r="E29" s="6">
+        <f>E18-E28</f>
+        <v/>
+      </c>
+      <c r="F29" s="6">
+        <f>F18-F28</f>
+        <v/>
+      </c>
+      <c r="G29" s="6">
+        <f>G18-G28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">　営業利益率</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr"/>
-      <c r="C29" s="38">
-        <f>IF(C12=0,0,C28/C12)</f>
-        <v/>
-      </c>
-      <c r="D29" s="38">
-        <f>IF(D12=0,0,D28/D12)</f>
-        <v/>
-      </c>
-      <c r="E29" s="38">
-        <f>IF(E12=0,0,E28/E12)</f>
-        <v/>
-      </c>
-      <c r="F29" s="38">
-        <f>IF(F12=0,0,F28/F12)</f>
-        <v/>
-      </c>
-      <c r="G29" s="38">
-        <f>IF(G12=0,0,G28/G12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="38">
+        <f>IF(C12=0,0,C29/C12)</f>
+        <v/>
+      </c>
+      <c r="D30" s="38">
+        <f>IF(D12=0,0,D29/D12)</f>
+        <v/>
+      </c>
+      <c r="E30" s="38">
+        <f>IF(E12=0,0,E29/E12)</f>
+        <v/>
+      </c>
+      <c r="F30" s="38">
+        <f>IF(F12=0,0,F29/F12)</f>
+        <v/>
+      </c>
+      <c r="G30" s="38">
+        <f>IF(G12=0,0,G29/G12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>投資家が見る指標</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>社員数</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr"/>
-      <c r="C32" s="8">
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="8">
         <f>'人員と人件費'!C10</f>
         <v/>
       </c>
-      <c r="D32" s="8">
+      <c r="D33" s="8">
         <f>'人員と人件費'!D10</f>
         <v/>
       </c>
-      <c r="E32" s="8">
+      <c r="E33" s="8">
         <f>'人員と人件費'!E10</f>
         <v/>
       </c>
-      <c r="F32" s="8">
+      <c r="F33" s="8">
         <f>'人員と人件費'!F10</f>
         <v/>
       </c>
-      <c r="G32" s="8">
+      <c r="G33" s="8">
         <f>'人員と人件費'!G10</f>
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>売上 / 社員（万円）</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr"/>
-      <c r="C33" s="6">
-        <f>IF(C32=0,0,C12*100/C32)</f>
-        <v/>
-      </c>
-      <c r="D33" s="6">
-        <f>IF(D32=0,0,D12*100/D32)</f>
-        <v/>
-      </c>
-      <c r="E33" s="6">
-        <f>IF(E32=0,0,E12*100/E32)</f>
-        <v/>
-      </c>
-      <c r="F33" s="6">
-        <f>IF(F32=0,0,F12*100/F32)</f>
-        <v/>
-      </c>
-      <c r="G33" s="6">
-        <f>IF(G32=0,0,G12*100/G32)</f>
-        <v/>
-      </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr"/>
+      <c r="C34" s="6">
+        <f>IF(C33=0,0,C12*100/C33)</f>
+        <v/>
+      </c>
+      <c r="D34" s="6">
+        <f>IF(D33=0,0,D12*100/D33)</f>
+        <v/>
+      </c>
+      <c r="E34" s="6">
+        <f>IF(E33=0,0,E12*100/E33)</f>
+        <v/>
+      </c>
+      <c r="F34" s="6">
+        <f>IF(F33=0,0,F12*100/F33)</f>
+        <v/>
+      </c>
+      <c r="G34" s="6">
+        <f>IF(G33=0,0,G12*100/G33)</f>
+        <v/>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>国内SaaSの平均2,000〜4,000万との比較</t>
         </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>研究開発費 ÷ 売上</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr"/>
-      <c r="C34" s="10">
-        <f>IF(C12=0,0,C22/C12)</f>
-        <v/>
-      </c>
-      <c r="D34" s="10">
-        <f>IF(D12=0,0,D22/D12)</f>
-        <v/>
-      </c>
-      <c r="E34" s="10">
-        <f>IF(E12=0,0,E22/E12)</f>
-        <v/>
-      </c>
-      <c r="F34" s="10">
-        <f>IF(F12=0,0,F22/F12)</f>
-        <v/>
-      </c>
-      <c r="G34" s="10">
-        <f>IF(G12=0,0,G22/G12)</f>
-        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
+          <t>研究開発費 ÷ 売上</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr"/>
+      <c r="C35" s="10">
+        <f>IF(C12=0,0,C23/C12)</f>
+        <v/>
+      </c>
+      <c r="D35" s="10">
+        <f>IF(D12=0,0,D23/D12)</f>
+        <v/>
+      </c>
+      <c r="E35" s="10">
+        <f>IF(E12=0,0,E23/E12)</f>
+        <v/>
+      </c>
+      <c r="F35" s="10">
+        <f>IF(F12=0,0,F23/F12)</f>
+        <v/>
+      </c>
+      <c r="G35" s="10">
+        <f>IF(G12=0,0,G23/G12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
           <t>人手に比例しない収益</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr"/>
-      <c r="C35" s="8">
+      <c r="B36" s="5" t="inlineStr"/>
+      <c r="C36" s="8">
         <f>C10+C11+C4*(1-1/'前提'!$C$4)</f>
         <v/>
       </c>
-      <c r="D35" s="8">
+      <c r="D36" s="8">
         <f>D10+D11+D4*(1-1/'前提'!$D$4)</f>
         <v/>
       </c>
-      <c r="E35" s="8">
+      <c r="E36" s="8">
         <f>E10+E11+E4*(1-1/'前提'!$E$4)</f>
         <v/>
       </c>
-      <c r="F35" s="8">
+      <c r="F36" s="8">
         <f>F10+F11+F4*(1-1/'前提'!$F$4)</f>
         <v/>
       </c>
-      <c r="G35" s="8">
+      <c r="G36" s="8">
         <f>G10+G11+G4*(1-1/'前提'!$G$4)</f>
         <v/>
       </c>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>②＋③＋①のうちAXで人手から切れた分</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">　同 比率</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr"/>
-      <c r="C36" s="9">
-        <f>IF(C12=0,0,C35/C12)</f>
-        <v/>
-      </c>
-      <c r="D36" s="9">
-        <f>IF(D12=0,0,D35/D12)</f>
-        <v/>
-      </c>
-      <c r="E36" s="9">
-        <f>IF(E12=0,0,E35/E12)</f>
-        <v/>
-      </c>
-      <c r="F36" s="9">
-        <f>IF(F12=0,0,F35/F12)</f>
-        <v/>
-      </c>
-      <c r="G36" s="9">
-        <f>IF(G12=0,0,G35/G12)</f>
-        <v/>
-      </c>
-      <c r="H36" s="7" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr"/>
+      <c r="C37" s="9">
+        <f>IF(C12=0,0,C36/C12)</f>
+        <v/>
+      </c>
+      <c r="D37" s="9">
+        <f>IF(D12=0,0,D36/D12)</f>
+        <v/>
+      </c>
+      <c r="E37" s="9">
+        <f>IF(E12=0,0,E36/E12)</f>
+        <v/>
+      </c>
+      <c r="F37" s="9">
+        <f>IF(F12=0,0,F36/F12)</f>
+        <v/>
+      </c>
+      <c r="G37" s="9">
+        <f>IF(G12=0,0,G36/G12)</f>
+        <v/>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>受託と読まれないための中心指標</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>顧客が浮かせる額</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr"/>
-      <c r="C37" s="8">
+      <c r="B38" s="5" t="inlineStr"/>
+      <c r="C38" s="8">
         <f>'商品マスタ①'!I14</f>
         <v/>
       </c>
-      <c r="D37" s="8">
+      <c r="D38" s="8">
         <f>'商品マスタ①'!J14</f>
         <v/>
       </c>
-      <c r="E37" s="8">
+      <c r="E38" s="8">
         <f>'商品マスタ①'!K14</f>
         <v/>
       </c>
-      <c r="F37" s="8">
+      <c r="F38" s="8">
         <f>'商品マスタ①'!L14</f>
         <v/>
       </c>
-      <c r="G37" s="8">
+      <c r="G38" s="8">
         <f>'商品マスタ①'!M14</f>
         <v/>
       </c>
-      <c r="H37" s="7" t="inlineStr">
+      <c r="H38" s="7" t="inlineStr">
         <is>
           <t>①の提案の中身。値引き額の総額</t>
         </is>
@@ -2669,23 +2702,23 @@
       </c>
       <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="37">
-        <f>'損益計算書'!C28</f>
+        <f>'損益計算書'!C29</f>
         <v/>
       </c>
       <c r="D4" s="37">
-        <f>'損益計算書'!D28</f>
+        <f>'損益計算書'!D29</f>
         <v/>
       </c>
       <c r="E4" s="37">
-        <f>'損益計算書'!E28</f>
+        <f>'損益計算書'!E29</f>
         <v/>
       </c>
       <c r="F4" s="37">
-        <f>'損益計算書'!F28</f>
+        <f>'損益計算書'!F29</f>
         <v/>
       </c>
       <c r="G4" s="37">
-        <f>'損益計算書'!G28</f>
+        <f>'損益計算書'!G29</f>
         <v/>
       </c>
     </row>
@@ -10325,7 +10358,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>下限はクリエイターの留保価格（工数×時給÷(1−手数料)）。上限は日本の発注者の支払意思。両側から挟まれた中で価格が決まる。★上限・工数・件数は提案値。</t>
+          <t>下限はクリエイターの留保価格（標準工数×時給÷(1−手数料)）。上限は日本の発注者の支払意思。工数は旧maxを標準に置き直した（ミニマムの見立てが甘かったため）。★上限・工数・件数は提案値。</t>
         </is>
       </c>
     </row>
@@ -10342,12 +10375,12 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>工数min</t>
+          <t>参考 軽い場合</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>工数max</t>
+          <t>標準工数</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -10404,7 +10437,7 @@
         <v>1.5</v>
       </c>
       <c r="E5" s="23">
-        <f>ROUNDUP('クリエイター経済'!$B$10*C5/(1-$B$26)/500,0)*500</f>
+        <f>ROUNDUP('クリエイター経済'!$B$10*D5/(1-$B$26)/500,0)*500</f>
         <v/>
       </c>
       <c r="F5" s="18" t="n">
@@ -10418,7 +10451,7 @@
         <v>25000</v>
       </c>
       <c r="I5" s="8">
-        <f>(C5+D5)/2*H5</f>
+        <f>D5*H5</f>
         <v/>
       </c>
       <c r="J5" s="29">
@@ -10449,7 +10482,7 @@
         <v>2.5</v>
       </c>
       <c r="E6" s="23">
-        <f>ROUNDUP('クリエイター経済'!$B$10*C6/(1-$B$26)/500,0)*500</f>
+        <f>ROUNDUP('クリエイター経済'!$B$10*D6/(1-$B$26)/500,0)*500</f>
         <v/>
       </c>
       <c r="F6" s="18" t="n">
@@ -10463,7 +10496,7 @@
         <v>12000</v>
       </c>
       <c r="I6" s="8">
-        <f>(C6+D6)/2*H6</f>
+        <f>D6*H6</f>
         <v/>
       </c>
       <c r="J6" s="29">
@@ -10494,7 +10527,7 @@
         <v>3</v>
       </c>
       <c r="E7" s="23">
-        <f>ROUNDUP('クリエイター経済'!$B$10*C7/(1-$B$26)/500,0)*500</f>
+        <f>ROUNDUP('クリエイター経済'!$B$10*D7/(1-$B$26)/500,0)*500</f>
         <v/>
       </c>
       <c r="F7" s="18" t="n">
@@ -10508,7 +10541,7 @@
         <v>8000</v>
       </c>
       <c r="I7" s="8">
-        <f>(C7+D7)/2*H7</f>
+        <f>D7*H7</f>
         <v/>
       </c>
       <c r="J7" s="29">
@@ -10539,7 +10572,7 @@
         <v>5</v>
       </c>
       <c r="E8" s="23">
-        <f>ROUNDUP('クリエイター経済'!$B$10*C8/(1-$B$26)/500,0)*500</f>
+        <f>ROUNDUP('クリエイター経済'!$B$10*D8/(1-$B$26)/500,0)*500</f>
         <v/>
       </c>
       <c r="F8" s="18" t="n">
@@ -10553,7 +10586,7 @@
         <v>10000</v>
       </c>
       <c r="I8" s="8">
-        <f>(C8+D8)/2*H8</f>
+        <f>D8*H8</f>
         <v/>
       </c>
       <c r="J8" s="29">
@@ -10584,7 +10617,7 @@
         <v>8</v>
       </c>
       <c r="E9" s="23">
-        <f>ROUNDUP('クリエイター経済'!$B$10*C9/(1-$B$26)/500,0)*500</f>
+        <f>ROUNDUP('クリエイター経済'!$B$10*D9/(1-$B$26)/500,0)*500</f>
         <v/>
       </c>
       <c r="F9" s="18" t="n">
@@ -10598,7 +10631,7 @@
         <v>6000</v>
       </c>
       <c r="I9" s="8">
-        <f>(C9+D9)/2*H9</f>
+        <f>D9*H9</f>
         <v/>
       </c>
       <c r="J9" s="29">
@@ -10629,7 +10662,7 @@
         <v>15</v>
       </c>
       <c r="E10" s="23">
-        <f>ROUNDUP('クリエイター経済'!$B$10*C10/(1-$B$26)/500,0)*500</f>
+        <f>ROUNDUP('クリエイター経済'!$B$10*D10/(1-$B$26)/500,0)*500</f>
         <v/>
       </c>
       <c r="F10" s="18" t="n">
@@ -10643,7 +10676,7 @@
         <v>9000</v>
       </c>
       <c r="I10" s="8">
-        <f>(C10+D10)/2*H10</f>
+        <f>D10*H10</f>
         <v/>
       </c>
       <c r="J10" s="29">
@@ -10674,7 +10707,7 @@
         <v>12</v>
       </c>
       <c r="E11" s="23">
-        <f>ROUNDUP('クリエイター経済'!$B$10*C11/(1-$B$26)/500,0)*500</f>
+        <f>ROUNDUP('クリエイター経済'!$B$10*D11/(1-$B$26)/500,0)*500</f>
         <v/>
       </c>
       <c r="F11" s="18" t="n">
@@ -10688,7 +10721,7 @@
         <v>4000</v>
       </c>
       <c r="I11" s="8">
-        <f>(C11+D11)/2*H11</f>
+        <f>D11*H11</f>
         <v/>
       </c>
       <c r="J11" s="29">
@@ -10719,7 +10752,7 @@
         <v>16</v>
       </c>
       <c r="E12" s="23">
-        <f>ROUNDUP('クリエイター経済'!$B$10*C12/(1-$B$26)/500,0)*500</f>
+        <f>ROUNDUP('クリエイター経済'!$B$10*D12/(1-$B$26)/500,0)*500</f>
         <v/>
       </c>
       <c r="F12" s="18" t="n">
@@ -10733,7 +10766,7 @@
         <v>2500</v>
       </c>
       <c r="I12" s="8">
-        <f>(C12+D12)/2*H12</f>
+        <f>D12*H12</f>
         <v/>
       </c>
       <c r="J12" s="29">
@@ -10764,7 +10797,7 @@
         <v>14</v>
       </c>
       <c r="E13" s="23">
-        <f>ROUNDUP('クリエイター経済'!$B$10*C13/(1-$B$26)/500,0)*500</f>
+        <f>ROUNDUP('クリエイター経済'!$B$10*D13/(1-$B$26)/500,0)*500</f>
         <v/>
       </c>
       <c r="F13" s="18" t="n">
@@ -10778,7 +10811,7 @@
         <v>5000</v>
       </c>
       <c r="I13" s="8">
-        <f>(C13+D13)/2*H13</f>
+        <f>D13*H13</f>
         <v/>
       </c>
       <c r="J13" s="29">
@@ -10809,7 +10842,7 @@
         <v>10</v>
       </c>
       <c r="E14" s="23">
-        <f>ROUNDUP('クリエイター経済'!$B$10*C14/(1-$B$26)/500,0)*500</f>
+        <f>ROUNDUP('クリエイター経済'!$B$10*D14/(1-$B$26)/500,0)*500</f>
         <v/>
       </c>
       <c r="F14" s="18" t="n">
@@ -10823,7 +10856,7 @@
         <v>3500</v>
       </c>
       <c r="I14" s="8">
-        <f>(C14+D14)/2*H14</f>
+        <f>D14*H14</f>
         <v/>
       </c>
       <c r="J14" s="29">
@@ -10854,7 +10887,7 @@
         <v>9</v>
       </c>
       <c r="E15" s="23">
-        <f>ROUNDUP('クリエイター経済'!$B$10*C15/(1-$B$26)/500,0)*500</f>
+        <f>ROUNDUP('クリエイター経済'!$B$10*D15/(1-$B$26)/500,0)*500</f>
         <v/>
       </c>
       <c r="F15" s="18" t="n">
@@ -10868,7 +10901,7 @@
         <v>2000</v>
       </c>
       <c r="I15" s="8">
-        <f>(C15+D15)/2*H15</f>
+        <f>D15*H15</f>
         <v/>
       </c>
       <c r="J15" s="29">
@@ -10899,7 +10932,7 @@
         <v>12</v>
       </c>
       <c r="E16" s="23">
-        <f>ROUNDUP('クリエイター経済'!$B$10*C16/(1-$B$26)/500,0)*500</f>
+        <f>ROUNDUP('クリエイター経済'!$B$10*D16/(1-$B$26)/500,0)*500</f>
         <v/>
       </c>
       <c r="F16" s="18" t="n">
@@ -10913,7 +10946,7 @@
         <v>6000</v>
       </c>
       <c r="I16" s="8">
-        <f>(C16+D16)/2*H16</f>
+        <f>D16*H16</f>
         <v/>
       </c>
       <c r="J16" s="29">
@@ -10944,7 +10977,7 @@
         <v>10</v>
       </c>
       <c r="E17" s="23">
-        <f>ROUNDUP('クリエイター経済'!$B$10*C17/(1-$B$26)/500,0)*500</f>
+        <f>ROUNDUP('クリエイター経済'!$B$10*D17/(1-$B$26)/500,0)*500</f>
         <v/>
       </c>
       <c r="F17" s="18" t="n">
@@ -10958,7 +10991,7 @@
         <v>8000</v>
       </c>
       <c r="I17" s="8">
-        <f>(C17+D17)/2*H17</f>
+        <f>D17*H17</f>
         <v/>
       </c>
       <c r="J17" s="29">
@@ -10989,7 +11022,7 @@
         <v>50</v>
       </c>
       <c r="E18" s="23">
-        <f>ROUNDUP('クリエイター経済'!$B$10*C18/(1-$B$26)/500,0)*500</f>
+        <f>ROUNDUP('クリエイター経済'!$B$10*D18/(1-$B$26)/500,0)*500</f>
         <v/>
       </c>
       <c r="F18" s="18" t="n">
@@ -11003,7 +11036,7 @@
         <v>12000</v>
       </c>
       <c r="I18" s="8">
-        <f>(C18+D18)/2*H18</f>
+        <f>D18*H18</f>
         <v/>
       </c>
       <c r="J18" s="29">
@@ -11680,7 +11713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -11696,14 +11729,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>人員と人件費（社員は極小）</t>
+          <t>人員と人件費（社員はPM中心）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>制作ディレクション・CS・オペレーションは社員ではなく業務委託／BPO。社員は経営・モデル開発・各機能の統括・管理のみ。</t>
+          <t>開発は中国・ベトナム・東欧への業務委託。社員として抱えるのはPM。制作ディレクション・CS・オペレーションも業務委託／BPO。管理はAX化で極小。</t>
         </is>
       </c>
     </row>
@@ -11782,30 +11815,30 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>モデル開発エンジニア</t>
+          <t>モデル開発PM</t>
         </is>
       </c>
       <c r="B5" s="18" t="n">
-        <v>850</v>
+        <v>950</v>
       </c>
       <c r="C5" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="E5" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="E5" s="18" t="n">
-        <v>16</v>
-      </c>
-      <c r="F5" s="18" t="n">
-        <v>28</v>
-      </c>
       <c r="G5" s="18" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>AX倍率を上げ続ける中核</t>
+          <t>オフショアチームを率いる。開発者は社員で抱えない</t>
         </is>
       </c>
     </row>
@@ -11915,17 +11948,17 @@
         <v>1</v>
       </c>
       <c r="E9" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="18" t="n">
-        <v>4</v>
-      </c>
       <c r="G9" s="18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>経理・法務・上場準備</t>
+          <t>AX化で極小。取引処理はBPOと自動化</t>
         </is>
       </c>
     </row>
@@ -12100,6 +12133,325 @@
       <c r="H17" s="7" t="inlineStr">
         <is>
           <t>クリエイター経済シート。①③の合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>オフショア開発（業務委託）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>値</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>単位</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>出所</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>ベトナム シニアエンジニア</t>
+        </is>
+      </c>
+      <c r="B21" s="25" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>万円/月</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>オフショア開発.com 2024（実測）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>中国（ベトナム比）</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>倍</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>★推定</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>東欧（ベトナム比）</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>倍</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>★推定</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>構成比 ベトナム</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>構成比 中国</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>構成比 東欧</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>加重単価（万円/年）</t>
+        </is>
+      </c>
+      <c r="B27" s="21">
+        <f>(B21*B24+B21*B22*B25+B21*B23*B26)*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>PM1名あたりのエンジニア数</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>★ブリッジはPMが兼ねる前提</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>期別</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr"/>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>1期</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>2期</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>3期</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>4期</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>5期</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>考え方</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>PM（社員）</t>
+        </is>
+      </c>
+      <c r="C32" s="8">
+        <f>C5</f>
+        <v/>
+      </c>
+      <c r="D32" s="8">
+        <f>D5</f>
+        <v/>
+      </c>
+      <c r="E32" s="8">
+        <f>E5</f>
+        <v/>
+      </c>
+      <c r="F32" s="8">
+        <f>F5</f>
+        <v/>
+      </c>
+      <c r="G32" s="8">
+        <f>G5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>オフショアエンジニア（委託）</t>
+        </is>
+      </c>
+      <c r="C33" s="8">
+        <f>C32*$B$28</f>
+        <v/>
+      </c>
+      <c r="D33" s="8">
+        <f>D32*$B$28</f>
+        <v/>
+      </c>
+      <c r="E33" s="8">
+        <f>E32*$B$28</f>
+        <v/>
+      </c>
+      <c r="F33" s="8">
+        <f>F32*$B$28</f>
+        <v/>
+      </c>
+      <c r="G33" s="8">
+        <f>G32*$B$28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>開発委託費（百万円）</t>
+        </is>
+      </c>
+      <c r="C34" s="6">
+        <f>C33*$B$27/100</f>
+        <v/>
+      </c>
+      <c r="D34" s="6">
+        <f>D33*$B$27/100</f>
+        <v/>
+      </c>
+      <c r="E34" s="6">
+        <f>E33*$B$27/100</f>
+        <v/>
+      </c>
+      <c r="F34" s="6">
+        <f>F33*$B$27/100</f>
+        <v/>
+      </c>
+      <c r="G34" s="6">
+        <f>G33*$B$27/100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>旧構成はモデル開発エンジニアを社員で40名抱えていた。PM8名＋委託40名に置き換えると、社員は61名→25名。コストはほぼ変わらない（人件費が下がり委託費が上がる）。狙いはコスト削減ではなく組織の身軽さ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="36" t="inlineStr">
+        <is>
+          <t>⚠ 管理・コーポレート2名は、5期に上場会社として内部統制報告制度の対象になる規模には薄い。取引処理はBPOに出す前提だが、内部統制の設計・運用・評価は社員の仕事。監査法人と主幹事に早期に当てること。★確認事項</t>
         </is>
       </c>
     </row>

--- a/事業計画_Ver1.5.xlsx
+++ b/事業計画_Ver1.5.xlsx
@@ -12172,11 +12172,11 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>ベトナム シニアエンジニア</t>
+          <t>ベトナム（シニア）</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
-        <v>48.3</v>
+        <v>50</v>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
@@ -12185,47 +12185,47 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>オフショア開発.com 2024（実測）</t>
+          <t>オフショア開発.com 2026（実測）</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>中国（ベトナム比）</t>
+          <t>中国（シニア）</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
-        <v>1.3</v>
+        <v>71.7</v>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>倍</t>
+          <t>万円/月</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>★推定</t>
+          <t>同上。★オフショア先で最も高い</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>東欧（ベトナム比）</t>
+          <t>東欧（シニア）</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
-        <v>1.6</v>
+        <v>80</v>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>倍</t>
+          <t>万円/月</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>★推定</t>
+          <t>★推定。この調査に東欧は含まれない</t>
         </is>
       </c>
     </row>
@@ -12296,7 +12296,7 @@
         </is>
       </c>
       <c r="B27" s="21">
-        <f>(B21*B24+B21*B22*B25+B21*B23*B26)*12</f>
+        <f>(B21*B24+B22*B25+B23*B26)*12</f>
         <v/>
       </c>
     </row>
@@ -12312,6 +12312,13 @@
       <c r="H28" s="7" t="inlineStr">
         <is>
           <t>★ブリッジはPMが兼ねる前提</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="36" t="inlineStr">
+        <is>
+          <t>⚠ 中国はオフショア先として最も高い（71.7万/月・ベトナムの1.43倍）。「中国の方が安い」のは剪辑師（月18.8万・雇用ベース）の話で、エンジニアの受託単価ではない。インド45.0／フィリピン47.5／ミャンマー40.0 の方が安い。</t>
         </is>
       </c>
     </row>

--- a/事業計画_Ver1.5.xlsx
+++ b/事業計画_Ver1.5.xlsx
@@ -11713,7 +11713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -11954,11 +11954,11 @@
         <v>2</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>AX化で極小。取引処理はBPOと自動化</t>
+          <t>AX化で極小。取引処理はBPO、専門領域は社外の顧問</t>
         </is>
       </c>
     </row>
@@ -12462,6 +12462,234 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>社外の専門家を前提にするなら、その費用が見えている必要がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>管理3名で回るのは顧問弁護士・監査法人・社労士が外にいるから。その費用は「その他販管費（売上の4%）」に入っている。5期で足りるかの検算。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>費目</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>下限</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>上限</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr"/>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>監査報酬（上場後）</t>
+        </is>
+      </c>
+      <c r="B42" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="C42" s="18" t="n">
+        <v>70</v>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>上場会社・売上108億規模</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>株式事務代行・IR</t>
+        </is>
+      </c>
+      <c r="B43" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>信託銀行・開示書類・説明会</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>顧問弁護士</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="C44" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>契約審査・中国パートナー・業務委託設計</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>税理士・社会保険労務士</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C45" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="H45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>オフィス（社員26名）</t>
+        </is>
+      </c>
+      <c r="B46" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="C46" s="18" t="n">
+        <v>50</v>
+      </c>
+      <c r="H46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>SaaS・通信・インフラ（非開発）</t>
+        </is>
+      </c>
+      <c r="B47" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="C47" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="H47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>採用・教育</t>
+        </is>
+      </c>
+      <c r="B48" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="C48" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>PM・統括級の採用は単価が高い</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>旅費交通</t>
+        </is>
+      </c>
+      <c r="B49" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="C49" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>中国・ベトナム・東欧の往復</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>保険・その他</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="C50" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="H50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>合計（百万円）</t>
+        </is>
+      </c>
+      <c r="B51" s="21">
+        <f>SUM(B42:B50)</f>
+        <v/>
+      </c>
+      <c r="C51" s="21">
+        <f>SUM(C42:C50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>その他販管費（5期・売上の4%）</t>
+        </is>
+      </c>
+      <c r="C52" s="6">
+        <f>'損益計算書'!G27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="C53" s="34">
+        <f>IF(C52&gt;=C51,"○ 上限まで賄える","× 足りない")</f>
+        <v/>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>★費目はすべて私の見積もり。実際の見積を取ったものではない</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/事業計画_Ver1.5.xlsx
+++ b/事業計画_Ver1.5.xlsx
@@ -2164,23 +2164,23 @@
       </c>
       <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="8">
-        <f>'人員と人件費'!C34</f>
+        <f>'人員と人件費'!C35</f>
         <v/>
       </c>
       <c r="D22" s="8">
-        <f>'人員と人件費'!D34</f>
+        <f>'人員と人件費'!D35</f>
         <v/>
       </c>
       <c r="E22" s="8">
-        <f>'人員と人件費'!E34</f>
+        <f>'人員と人件費'!E35</f>
         <v/>
       </c>
       <c r="F22" s="8">
-        <f>'人員と人件費'!F34</f>
+        <f>'人員と人件費'!F35</f>
         <v/>
       </c>
       <c r="G22" s="8">
-        <f>'人員と人件費'!G34</f>
+        <f>'人員と人件費'!G35</f>
         <v/>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -11713,7 +11713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -11821,24 +11821,29 @@
       <c r="B5" s="18" t="n">
         <v>950</v>
       </c>
-      <c r="C5" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" s="18" t="n">
-        <v>8</v>
+      <c r="C5" s="21">
+        <f>C34</f>
+        <v/>
+      </c>
+      <c r="D5" s="21">
+        <f>D34</f>
+        <v/>
+      </c>
+      <c r="E5" s="21">
+        <f>E34</f>
+        <v/>
+      </c>
+      <c r="F5" s="21">
+        <f>F34</f>
+        <v/>
+      </c>
+      <c r="G5" s="21">
+        <f>G34</f>
+        <v/>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>オフショアチームを率いる。開発者は社員で抱えない</t>
+          <t>オフショアチームを率いる。人数はAX後のエンジニア数から逆算</t>
         </is>
       </c>
     </row>
@@ -12139,27 +12144,31 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>オフショア開発（業務委託）</t>
+          <t>オフショア開発（業務委託）— 単価は国別の実測</t>
         </is>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>項目</t>
+          <t>国</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>値</t>
+          <t>シニア(万/月)</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>単位</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr"/>
+          <t>リード(万/月)</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>構成比</t>
+        </is>
+      </c>
       <c r="E20" s="3" t="inlineStr"/>
       <c r="F20" s="3" t="inlineStr"/>
       <c r="G20" s="3" t="inlineStr"/>
@@ -12172,454 +12181,447 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>ベトナム（シニア）</t>
+          <t>ベトナム</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
         <v>50</v>
       </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>万円/月</t>
-        </is>
+      <c r="C21" s="25" t="n">
+        <v>59</v>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>0.5</v>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>オフショア開発.com 2026（実測）</t>
+          <t>オフショア開発.com 2026（シニア／ブリッジSE）</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>中国（シニア）</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
         <v>71.7</v>
       </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>万円/月</t>
-        </is>
+      <c r="C22" s="25" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>0.3</v>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>同上。★オフショア先で最も高い</t>
+          <t>同上。アジアでは最も高い</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>東欧（シニア）</t>
+          <t>東欧</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
-        <v>80</v>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>万円/月</t>
-        </is>
+        <v>104</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>124.8</v>
+      </c>
+      <c r="D23" s="19" t="n">
+        <v>0.2</v>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>★推定。この調査に東欧は含まれない</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>構成比 ベトナム</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>★</t>
+          <t>Devico/RemoteMore/Wild.Codes 2026。羅$30-45・宇$40-55・波$35-55/h を月160h・150円換算</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>構成比 中国</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>シニア級 加重（万円/年）</t>
+        </is>
+      </c>
+      <c r="B25" s="23">
+        <f>SUMPRODUCT(B21:B23,D21:D23)*12</f>
+        <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>構成比 東欧</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>リード級 加重（万円/年）</t>
+        </is>
+      </c>
+      <c r="B26" s="6">
+        <f>SUMPRODUCT(C21:C23,D21:D23)*12</f>
+        <v/>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>AX前提はこちらを使う。人数を減らすかわりに上位層に絞る</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>加重単価（万円/年）</t>
-        </is>
-      </c>
-      <c r="B27" s="21">
-        <f>(B21*B24+B22*B25+B23*B26)*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>PM1名あたりのエンジニア数</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="n">
+      <c r="A27" s="36" t="inlineStr">
+        <is>
+          <t>⚠ 安い順は ミャンマー＜インド＜フィリピン＜ベトナム＜中国＜東欧。中国も東欧もアジア最安ではない。「中国が安い」のは剪辑師（月18.8万）の話で、エンジニアの受託単価ではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>エンジニアのAX化 — 人数を減らして単価を上げる</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>1期</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>2期</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>3期</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>4期</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>5期</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>考え方</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>必要開発工数（AXなし換算・人年）</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>★ブリッジはPMが兼ねる前提</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="36" t="inlineStr">
-        <is>
-          <t>⚠ 中国はオフショア先として最も高い（71.7万/月・ベトナムの1.43倍）。「中国の方が安い」のは剪辑師（月18.8万・雇用ベース）の話で、エンジニアの受託単価ではない。インド45.0／フィリピン47.5／ミャンマー40.0 の方が安い。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>期別</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr"/>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>1期</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>2期</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>3期</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>4期</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>5期</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>考え方</t>
+      <c r="D31" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F31" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="G31" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>★プロダクト規模から</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>PM（社員）</t>
-        </is>
-      </c>
-      <c r="C32" s="8">
-        <f>C5</f>
-        <v/>
-      </c>
-      <c r="D32" s="8">
-        <f>D5</f>
-        <v/>
-      </c>
-      <c r="E32" s="8">
-        <f>E5</f>
-        <v/>
-      </c>
-      <c r="F32" s="8">
-        <f>F5</f>
-        <v/>
-      </c>
-      <c r="G32" s="8">
-        <f>G5</f>
-        <v/>
+          <t>★ エンジニアのAX倍率</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E32" s="25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F32" s="25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G32" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>★制作のAX（5期4.0倍）より保守的に置く</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>オフショアエンジニア（委託）</t>
-        </is>
-      </c>
-      <c r="C33" s="8">
-        <f>C32*$B$28</f>
-        <v/>
-      </c>
-      <c r="D33" s="8">
-        <f>D32*$B$28</f>
-        <v/>
-      </c>
-      <c r="E33" s="8">
-        <f>E32*$B$28</f>
-        <v/>
-      </c>
-      <c r="F33" s="8">
-        <f>F32*$B$28</f>
-        <v/>
-      </c>
-      <c r="G33" s="8">
-        <f>G32*$B$28</f>
-        <v/>
+          <t>実エンジニア数（委託）</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="23">
+        <f>ROUNDUP(C31/C32,0)</f>
+        <v/>
+      </c>
+      <c r="D33" s="23">
+        <f>ROUNDUP(D31/D32,0)</f>
+        <v/>
+      </c>
+      <c r="E33" s="23">
+        <f>ROUNDUP(E31/E32,0)</f>
+        <v/>
+      </c>
+      <c r="F33" s="23">
+        <f>ROUNDUP(F31/F32,0)</f>
+        <v/>
+      </c>
+      <c r="G33" s="23">
+        <f>ROUNDUP(G31/G32,0)</f>
+        <v/>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>必要工数 ÷ AX倍率</t>
+        </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>PM（社員）</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr"/>
+      <c r="C34" s="23">
+        <f>ROUNDUP(C33/5,0)</f>
+        <v/>
+      </c>
+      <c r="D34" s="23">
+        <f>ROUNDUP(D33/5,0)</f>
+        <v/>
+      </c>
+      <c r="E34" s="23">
+        <f>ROUNDUP(E33/5,0)</f>
+        <v/>
+      </c>
+      <c r="F34" s="23">
+        <f>ROUNDUP(F33/5,0)</f>
+        <v/>
+      </c>
+      <c r="G34" s="23">
+        <f>ROUNDUP(G33/5,0)</f>
+        <v/>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>1名で5名を見る。上の人件費表はここを参照</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>開発委託費（百万円）</t>
         </is>
       </c>
-      <c r="C34" s="6">
-        <f>C33*$B$27/100</f>
-        <v/>
-      </c>
-      <c r="D34" s="6">
-        <f>D33*$B$27/100</f>
-        <v/>
-      </c>
-      <c r="E34" s="6">
-        <f>E33*$B$27/100</f>
-        <v/>
-      </c>
-      <c r="F34" s="6">
-        <f>F33*$B$27/100</f>
-        <v/>
-      </c>
-      <c r="G34" s="6">
-        <f>G33*$B$27/100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>旧構成はモデル開発エンジニアを社員で40名抱えていた。PM8名＋委託40名に置き換えると、社員は61名→25名。コストはほぼ変わらない（人件費が下がり委託費が上がる）。狙いはコスト削減ではなく組織の身軽さ。</t>
+      <c r="B35" s="5" t="inlineStr"/>
+      <c r="C35" s="6">
+        <f>C33*$B$26/100</f>
+        <v/>
+      </c>
+      <c r="D35" s="6">
+        <f>D33*$B$26/100</f>
+        <v/>
+      </c>
+      <c r="E35" s="6">
+        <f>E33*$B$26/100</f>
+        <v/>
+      </c>
+      <c r="F35" s="6">
+        <f>F33*$B$26/100</f>
+        <v/>
+      </c>
+      <c r="G35" s="6">
+        <f>G33*$B$26/100</f>
+        <v/>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>実人数 × リード級の年額</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="36" t="inlineStr">
-        <is>
-          <t>⚠ 管理・コーポレート2名は、5期に上場会社として内部統制報告制度の対象になる規模には薄い。取引処理はBPOに出す前提だが、内部統制の設計・運用・評価は社員の仕事。監査法人と主幹事に早期に当てること。★確認事項</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="12" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>旧構成は社員40名。PM4名＋委託16名になる。単価は年808万→926万に上げても、委託費は5期300→148百万。1〜2期は逆に高くつく（AX倍率が立つ前に単価だけ上がるため）。制作のAXと同じ形で、先に投資して後で効く。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
         <is>
           <t>社外の専門家を前提にするなら、その費用が見えている必要がある</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>管理3名で回るのは顧問弁護士・監査法人・社労士が外にいるから。その費用は「その他販管費（売上の4%）」に入っている。5期で足りるかの検算。</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>費目</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>下限</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>上限</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr"/>
+      <c r="E42" s="3" t="inlineStr"/>
+      <c r="F42" s="3" t="inlineStr"/>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>監査報酬（上場後）</t>
-        </is>
-      </c>
-      <c r="B42" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="C42" s="18" t="n">
-        <v>70</v>
-      </c>
-      <c r="H42" s="7" t="inlineStr">
-        <is>
-          <t>上場会社・売上108億規模</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>株式事務代行・IR</t>
+          <t>監査報酬（上場後）</t>
         </is>
       </c>
       <c r="B43" s="18" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C43" s="18" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>信託銀行・開示書類・説明会</t>
+          <t>上場会社・売上108億規模</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>顧問弁護士</t>
+          <t>株式事務代行・IR</t>
         </is>
       </c>
       <c r="B44" s="18" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C44" s="18" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>契約審査・中国パートナー・業務委託設計</t>
+          <t>信託銀行・開示書類・説明会</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>税理士・社会保険労務士</t>
+          <t>顧問弁護士</t>
         </is>
       </c>
       <c r="B45" s="18" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C45" s="18" t="n">
-        <v>12</v>
-      </c>
-      <c r="H45" s="7" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>契約審査・中国パートナー・業務委託設計</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>オフィス（社員26名）</t>
+          <t>税理士・社会保険労務士</t>
         </is>
       </c>
       <c r="B46" s="18" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C46" s="18" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="H46" s="7" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>SaaS・通信・インフラ（非開発）</t>
+          <t>オフィス（社員26名）</t>
         </is>
       </c>
       <c r="B47" s="18" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C47" s="18" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>採用・教育</t>
+          <t>SaaS・通信・インフラ（非開発）</t>
         </is>
       </c>
       <c r="B48" s="18" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C48" s="18" t="n">
-        <v>60</v>
-      </c>
-      <c r="H48" s="7" t="inlineStr">
-        <is>
-          <t>PM・統括級の採用は単価が高い</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="H48" s="7" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>旅費交通</t>
+          <t>採用・教育</t>
         </is>
       </c>
       <c r="B49" s="18" t="n">
@@ -12630,61 +12632,69 @@
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>中国・ベトナム・東欧の往復</t>
+          <t>PM・統括級の採用は単価が高い</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
+          <t>旅費交通</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="C50" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>中国・ベトナム・東欧の往復</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
           <t>保険・その他</t>
         </is>
       </c>
-      <c r="B50" s="18" t="n">
+      <c r="B51" s="18" t="n">
         <v>20</v>
       </c>
-      <c r="C50" s="18" t="n">
+      <c r="C51" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="H50" s="7" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>合計（百万円）</t>
-        </is>
-      </c>
-      <c r="B51" s="21">
-        <f>SUM(B42:B50)</f>
-        <v/>
-      </c>
-      <c r="C51" s="21">
-        <f>SUM(C42:C50)</f>
-        <v/>
-      </c>
+      <c r="H51" s="7" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>その他販管費（5期・売上の4%）</t>
-        </is>
-      </c>
-      <c r="C52" s="6">
+      <c r="B52" s="21">
+        <f>SUM(B43:B51)</f>
+        <v/>
+      </c>
+      <c r="C52" s="21">
+        <f>SUM(C43:C51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" s="6">
         <f>'損益計算書'!G27</f>
         <v/>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
-      <c r="C53" s="34">
-        <f>IF(C52&gt;=C51,"○ 上限まで賄える","× 足りない")</f>
-        <v/>
-      </c>
-      <c r="H53" s="7" t="inlineStr">
+      <c r="C54" s="34">
+        <f>IF(C53&gt;=C52,"○ 上限まで賄える","× 足りない")</f>
+        <v/>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
         <is>
           <t>★費目はすべて私の見積もり。実際の見積を取ったものではない</t>
         </is>

--- a/事業計画_Ver1.5.xlsx
+++ b/事業計画_Ver1.5.xlsx
@@ -2164,23 +2164,23 @@
       </c>
       <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="8">
-        <f>'人員と人件費'!C35</f>
+        <f>'人員と人件費'!C36</f>
         <v/>
       </c>
       <c r="D22" s="8">
-        <f>'人員と人件費'!D35</f>
+        <f>'人員と人件費'!D36</f>
         <v/>
       </c>
       <c r="E22" s="8">
-        <f>'人員と人件費'!E35</f>
+        <f>'人員と人件費'!E36</f>
         <v/>
       </c>
       <c r="F22" s="8">
-        <f>'人員と人件費'!F35</f>
+        <f>'人員と人件費'!F36</f>
         <v/>
       </c>
       <c r="G22" s="8">
-        <f>'人員と人件費'!G35</f>
+        <f>'人員と人件費'!G36</f>
         <v/>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -11822,23 +11822,23 @@
         <v>950</v>
       </c>
       <c r="C5" s="21">
-        <f>C34</f>
+        <f>C35</f>
         <v/>
       </c>
       <c r="D5" s="21">
-        <f>D34</f>
+        <f>D35</f>
         <v/>
       </c>
       <c r="E5" s="21">
-        <f>E34</f>
+        <f>E35</f>
         <v/>
       </c>
       <c r="F5" s="21">
-        <f>F34</f>
+        <f>F35</f>
         <v/>
       </c>
       <c r="G5" s="21">
-        <f>G34</f>
+        <f>G35</f>
         <v/>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -12271,212 +12271,219 @@
     <row r="27">
       <c r="A27" s="36" t="inlineStr">
         <is>
-          <t>⚠ 安い順は ミャンマー＜インド＜フィリピン＜ベトナム＜中国＜東欧。中国も東欧もアジア最安ではない。「中国が安い」のは剪辑師（月18.8万）の話で、エンジニアの受託単価ではない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+          <t>⚠ 安い順は ミャンマー(40)＜インド(45)＜フィリピン(47.5)＜ベトナム(50)＜中国(71.7)＜東欧(104)。「中国が安い」のは剪辑師（月18.8万）の話で、エンジニアの受託単価ではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="36" t="inlineStr">
+        <is>
+          <t>⚠ ロシア・ベラルーシは対象外。外為法の役務取引規制（2022/3/18〜）で経産大臣の許可制、限定的な例外を除き許可されない。送金も通らない。単価の問題ではなく、上場審査で主幹事・監査法人が必ず見る論点。ミャンマーは最安だが政情リスクで△。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>エンジニアのAX化 — 人数を減らして単価を上げる</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr"/>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr"/>
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>1期</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>2期</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>3期</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>4期</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>5期</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>考え方</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>必要開発工数（AXなし換算・人年）</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr"/>
-      <c r="C31" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="D31" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" s="18" t="n">
-        <v>20</v>
-      </c>
-      <c r="F31" s="18" t="n">
-        <v>30</v>
-      </c>
-      <c r="G31" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>★プロダクト規模から</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>★ エンジニアのAX倍率</t>
+          <t>必要開発工数（AXなし換算・人年）</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr"/>
-      <c r="C32" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E32" s="25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F32" s="25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="G32" s="25" t="n">
-        <v>2.5</v>
+      <c r="C32" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D32" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="G32" s="18" t="n">
+        <v>40</v>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>★制作のAX（5期4.0倍）より保守的に置く</t>
+          <t>★プロダクト規模から</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>実エンジニア数（委託）</t>
+          <t>★ エンジニアのAX倍率</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr"/>
-      <c r="C33" s="23">
-        <f>ROUNDUP(C31/C32,0)</f>
-        <v/>
-      </c>
-      <c r="D33" s="23">
-        <f>ROUNDUP(D31/D32,0)</f>
-        <v/>
-      </c>
-      <c r="E33" s="23">
-        <f>ROUNDUP(E31/E32,0)</f>
-        <v/>
-      </c>
-      <c r="F33" s="23">
-        <f>ROUNDUP(F31/F32,0)</f>
-        <v/>
-      </c>
-      <c r="G33" s="23">
-        <f>ROUNDUP(G31/G32,0)</f>
-        <v/>
+      <c r="C33" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E33" s="25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F33" s="25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G33" s="25" t="n">
+        <v>2.5</v>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>必要工数 ÷ AX倍率</t>
+          <t>★制作のAX（5期4.0倍）より保守的に置く</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>PM（社員）</t>
+          <t>実エンジニア数（委託）</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr"/>
       <c r="C34" s="23">
-        <f>ROUNDUP(C33/5,0)</f>
+        <f>ROUNDUP(C32/C33,0)</f>
         <v/>
       </c>
       <c r="D34" s="23">
-        <f>ROUNDUP(D33/5,0)</f>
+        <f>ROUNDUP(D32/D33,0)</f>
         <v/>
       </c>
       <c r="E34" s="23">
-        <f>ROUNDUP(E33/5,0)</f>
+        <f>ROUNDUP(E32/E33,0)</f>
         <v/>
       </c>
       <c r="F34" s="23">
-        <f>ROUNDUP(F33/5,0)</f>
+        <f>ROUNDUP(F32/F33,0)</f>
         <v/>
       </c>
       <c r="G34" s="23">
-        <f>ROUNDUP(G33/5,0)</f>
+        <f>ROUNDUP(G32/G33,0)</f>
         <v/>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
+          <t>必要工数 ÷ AX倍率</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>PM（社員）</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr"/>
+      <c r="C35" s="23">
+        <f>ROUNDUP(C34/5,0)</f>
+        <v/>
+      </c>
+      <c r="D35" s="23">
+        <f>ROUNDUP(D34/5,0)</f>
+        <v/>
+      </c>
+      <c r="E35" s="23">
+        <f>ROUNDUP(E34/5,0)</f>
+        <v/>
+      </c>
+      <c r="F35" s="23">
+        <f>ROUNDUP(F34/5,0)</f>
+        <v/>
+      </c>
+      <c r="G35" s="23">
+        <f>ROUNDUP(G34/5,0)</f>
+        <v/>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
           <t>1名で5名を見る。上の人件費表はここを参照</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>開発委託費（百万円）</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr"/>
-      <c r="C35" s="6">
-        <f>C33*$B$26/100</f>
-        <v/>
-      </c>
-      <c r="D35" s="6">
-        <f>D33*$B$26/100</f>
-        <v/>
-      </c>
-      <c r="E35" s="6">
-        <f>E33*$B$26/100</f>
-        <v/>
-      </c>
-      <c r="F35" s="6">
-        <f>F33*$B$26/100</f>
-        <v/>
-      </c>
-      <c r="G35" s="6">
-        <f>G33*$B$26/100</f>
-        <v/>
-      </c>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr"/>
+      <c r="C36" s="6">
+        <f>C34*$B$26/100</f>
+        <v/>
+      </c>
+      <c r="D36" s="6">
+        <f>D34*$B$26/100</f>
+        <v/>
+      </c>
+      <c r="E36" s="6">
+        <f>E34*$B$26/100</f>
+        <v/>
+      </c>
+      <c r="F36" s="6">
+        <f>F34*$B$26/100</f>
+        <v/>
+      </c>
+      <c r="G36" s="6">
+        <f>G34*$B$26/100</f>
+        <v/>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>実人数 × リード級の年額</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>旧構成は社員40名。PM4名＋委託16名になる。単価は年808万→926万に上げても、委託費は5期300→148百万。1〜2期は逆に高くつく（AX倍率が立つ前に単価だけ上がるため）。制作のAXと同じ形で、先に投資して後で効く。</t>
         </is>

--- a/事業計画_Ver1.5.xlsx
+++ b/事業計画_Ver1.5.xlsx
@@ -12191,92 +12191,113 @@
         <v>59</v>
       </c>
       <c r="D21" s="19" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>オフショア開発.com 2026（シニア／ブリッジSE）</t>
+          <t>オフショア開発.com 2026（シニア／ブリッジSE）。主軸</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>インド</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
-        <v>71.7</v>
+        <v>45</v>
       </c>
       <c r="C22" s="25" t="n">
-        <v>75.8</v>
+        <v>60</v>
       </c>
       <c r="D22" s="19" t="n">
         <v>0.3</v>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>同上。アジアでは最も高い</t>
+          <t>同上。ベトナムより1割安く、英語圏で層が厚い</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="D23" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>参考。高いため外した</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
           <t>東欧</t>
         </is>
       </c>
-      <c r="B23" s="25" t="n">
+      <c r="B24" s="25" t="n">
         <v>104</v>
       </c>
-      <c r="C23" s="25" t="n">
+      <c r="C24" s="25" t="n">
         <v>124.8</v>
       </c>
-      <c r="D23" s="19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>Devico/RemoteMore/Wild.Codes 2026。羅$30-45・宇$40-55・波$35-55/h を月160h・150円換算</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>シニア級 加重（万円/年）</t>
-        </is>
-      </c>
-      <c r="B25" s="23">
-        <f>SUMPRODUCT(B21:B23,D21:D23)*12</f>
-        <v/>
+      <c r="D24" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>参考。Devico/RemoteMore/Wild.Codes 2026（月160h・150円換算）。最も高いため外した</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
+          <t>シニア級 加重（万円/年）</t>
+        </is>
+      </c>
+      <c r="B26" s="23">
+        <f>SUMPRODUCT(B21:B24,D21:D24)*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
           <t>リード級 加重（万円/年）</t>
         </is>
       </c>
-      <c r="B26" s="6">
-        <f>SUMPRODUCT(C21:C23,D21:D23)*12</f>
-        <v/>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="B27" s="6">
+        <f>SUMPRODUCT(C21:C24,D21:D24)*12</f>
+        <v/>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>AX前提はこちらを使う。人数を減らすかわりに上位層に絞る</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="36" t="inlineStr">
-        <is>
-          <t>⚠ 安い順は ミャンマー(40)＜インド(45)＜フィリピン(47.5)＜ベトナム(50)＜中国(71.7)＜東欧(104)。「中国が安い」のは剪辑師（月18.8万）の話で、エンジニアの受託単価ではない。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="36" t="inlineStr">
+        <is>
+          <t>⚠ 安い順は ミャンマー(40)＜インド(45)＜フィリピン(47.5)＜ベトナム(50)＜中国(71.7)＜東欧(104)。「中国が安い」のは剪辑師（月18.8万）の話で、エンジニアの受託単価ではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="36" t="inlineStr">
         <is>
           <t>⚠ ロシア・ベラルーシは対象外。外為法の役務取引規制（2022/3/18〜）で経産大臣の許可制、限定的な例外を除き許可されない。送金も通らない。単価の問題ではなく、上場審査で主幹事・監査法人が必ず見る論点。ミャンマーは最安だが政情リスクで△。</t>
         </is>
@@ -12457,23 +12478,23 @@
       </c>
       <c r="B36" s="5" t="inlineStr"/>
       <c r="C36" s="6">
-        <f>C34*$B$26/100</f>
+        <f>C34*$B$27/100</f>
         <v/>
       </c>
       <c r="D36" s="6">
-        <f>D34*$B$26/100</f>
+        <f>D34*$B$27/100</f>
         <v/>
       </c>
       <c r="E36" s="6">
-        <f>E34*$B$26/100</f>
+        <f>E34*$B$27/100</f>
         <v/>
       </c>
       <c r="F36" s="6">
-        <f>F34*$B$26/100</f>
+        <f>F34*$B$27/100</f>
         <v/>
       </c>
       <c r="G36" s="6">
-        <f>G34*$B$26/100</f>
+        <f>G34*$B$27/100</f>
         <v/>
       </c>
       <c r="H36" s="7" t="inlineStr">

--- a/事業計画_Ver1.5.xlsx
+++ b/事業計画_Ver1.5.xlsx
@@ -234,10 +234,10 @@
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2164,23 +2164,23 @@
       </c>
       <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="8">
-        <f>'人員と人件費'!C36</f>
+        <f>'人員と人件費'!C38</f>
         <v/>
       </c>
       <c r="D22" s="8">
-        <f>'人員と人件費'!D36</f>
+        <f>'人員と人件費'!D38</f>
         <v/>
       </c>
       <c r="E22" s="8">
-        <f>'人員と人件費'!E36</f>
+        <f>'人員と人件費'!E38</f>
         <v/>
       </c>
       <c r="F22" s="8">
-        <f>'人員と人件費'!F36</f>
+        <f>'人員と人件費'!F38</f>
         <v/>
       </c>
       <c r="G22" s="8">
-        <f>'人員と人件費'!G36</f>
+        <f>'人員と人件費'!G38</f>
         <v/>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -2402,23 +2402,23 @@
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr"/>
-      <c r="C30" s="38">
+      <c r="C30" s="39">
         <f>IF(C12=0,0,C29/C12)</f>
         <v/>
       </c>
-      <c r="D30" s="38">
+      <c r="D30" s="39">
         <f>IF(D12=0,0,D29/D12)</f>
         <v/>
       </c>
-      <c r="E30" s="38">
+      <c r="E30" s="39">
         <f>IF(E12=0,0,E29/E12)</f>
         <v/>
       </c>
-      <c r="F30" s="38">
+      <c r="F30" s="39">
         <f>IF(F12=0,0,F29/F12)</f>
         <v/>
       </c>
-      <c r="G30" s="38">
+      <c r="G30" s="39">
         <f>IF(G12=0,0,G29/G12)</f>
         <v/>
       </c>
@@ -3586,7 +3586,7 @@
           <t>転換時のシード持分</t>
         </is>
       </c>
-      <c r="C15" s="39">
+      <c r="C15" s="38">
         <f>C7/C6</f>
         <v/>
       </c>
@@ -3602,7 +3602,7 @@
           <t>シリーズA の持分</t>
         </is>
       </c>
-      <c r="C16" s="39">
+      <c r="C16" s="38">
         <f>C10/C9</f>
         <v/>
       </c>
@@ -4035,7 +4035,7 @@
           <t>創業者（役員）</t>
         </is>
       </c>
-      <c r="B30" s="38">
+      <c r="B30" s="39">
         <f>D26</f>
         <v/>
       </c>
@@ -4049,7 +4049,7 @@
           <t>× 除外</t>
         </is>
       </c>
-      <c r="E30" s="38" t="n">
+      <c r="E30" s="39" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="7" t="inlineStr">
@@ -4064,7 +4064,7 @@
           <t>ESOP枠</t>
         </is>
       </c>
-      <c r="B31" s="38">
+      <c r="B31" s="39">
         <f>E26</f>
         <v/>
       </c>
@@ -4078,7 +4078,7 @@
           <t>× 除外</t>
         </is>
       </c>
-      <c r="E31" s="38" t="n">
+      <c r="E31" s="39" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="7" t="inlineStr">
@@ -4093,7 +4093,7 @@
           <t>シード投資家 保有分</t>
         </is>
       </c>
-      <c r="B32" s="38">
+      <c r="B32" s="39">
         <f>F26</f>
         <v/>
       </c>
@@ -4105,7 +4105,7 @@
         <f>IF(B32&lt;0.1,"○ 算入","× 除外")</f>
         <v/>
       </c>
-      <c r="E32" s="38">
+      <c r="E32" s="39">
         <f>IF(B32&lt;0.1,B32,0)</f>
         <v/>
       </c>
@@ -4121,7 +4121,7 @@
           <t>シリーズA 保有分</t>
         </is>
       </c>
-      <c r="B33" s="38">
+      <c r="B33" s="39">
         <f>G26</f>
         <v/>
       </c>
@@ -4133,7 +4133,7 @@
         <f>IF(B33&lt;0.1,"○ 算入","× 除外")</f>
         <v/>
       </c>
-      <c r="E33" s="38">
+      <c r="E33" s="39">
         <f>IF(B33&lt;0.1,B33,0)</f>
         <v/>
       </c>
@@ -4149,7 +4149,7 @@
           <t>公募・売出し</t>
         </is>
       </c>
-      <c r="B34" s="38">
+      <c r="B34" s="39">
         <f>H26</f>
         <v/>
       </c>
@@ -4163,7 +4163,7 @@
           <t>○ 算入</t>
         </is>
       </c>
-      <c r="E34" s="38">
+      <c r="E34" s="39">
         <f>B34</f>
         <v/>
       </c>
@@ -4330,7 +4330,7 @@
           <t>転換時のシード持分</t>
         </is>
       </c>
-      <c r="B6" s="39">
+      <c r="B6" s="38">
         <f>'資本構成の推移'!C15</f>
         <v/>
       </c>
@@ -4382,7 +4382,7 @@
           <t>上場後のシード持分</t>
         </is>
       </c>
-      <c r="B8" s="39">
+      <c r="B8" s="38">
         <f>'資本構成の推移'!F25</f>
         <v/>
       </c>
@@ -11713,7 +11713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -11822,23 +11822,23 @@
         <v>950</v>
       </c>
       <c r="C5" s="21">
-        <f>C35</f>
+        <f>C37</f>
         <v/>
       </c>
       <c r="D5" s="21">
-        <f>D35</f>
+        <f>D37</f>
         <v/>
       </c>
       <c r="E5" s="21">
-        <f>E35</f>
+        <f>E37</f>
         <v/>
       </c>
       <c r="F5" s="21">
-        <f>F35</f>
+        <f>F37</f>
         <v/>
       </c>
       <c r="G5" s="21">
-        <f>G35</f>
+        <f>G37</f>
         <v/>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -12144,548 +12144,525 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>オフショア開発（業務委託）— 単価は国別の実測</t>
+          <t>オフショア開発（業務委託）— ベトナム内のピラミッド</t>
         </is>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>国</t>
+          <t>国・職位</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>シニア(万/月)</t>
+          <t>月額(万)</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>リード(万/月)</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
           <t>構成比</t>
         </is>
       </c>
+      <c r="D20" s="3" t="inlineStr"/>
       <c r="E20" s="3" t="inlineStr"/>
       <c r="F20" s="3" t="inlineStr"/>
       <c r="G20" s="3" t="inlineStr"/>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>出所</t>
+          <t>出所・考え方</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>ベトナム</t>
+          <t>ベトナム ブリッジSE</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
-        <v>50</v>
-      </c>
-      <c r="C21" s="25" t="n">
         <v>59</v>
       </c>
-      <c r="D21" s="19" t="n">
-        <v>0.7</v>
+      <c r="C21" s="19" t="n">
+        <v>0.2</v>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>オフショア開発.com 2026（シニア／ブリッジSE）。主軸</t>
+          <t>オフショア開発.com 2026。レビューと設計を担う上位層</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>インド</t>
+          <t>ベトナム プログラマー</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
-        <v>45</v>
-      </c>
-      <c r="C22" s="25" t="n">
-        <v>60</v>
-      </c>
-      <c r="D22" s="19" t="n">
-        <v>0.3</v>
+        <v>40.1</v>
+      </c>
+      <c r="C22" s="19" t="n">
+        <v>0.8</v>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>同上。ベトナムより1割安く、英語圏で層が厚い</t>
+          <t>同上。実装を担う</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>インド ブリッジSE</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
-        <v>71.7</v>
-      </c>
-      <c r="C23" s="25" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="D23" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="C23" s="19" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>参考。高いため外した</t>
+          <t>参考。上位層で入れる場合</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>東欧</t>
+          <t>インド プログラマー</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="C24" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>参考。ミドルを別国にすると継ぎ目が増える</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>中国 シニア</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="C25" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>参考。ベトナムBSEより21%高い</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>東欧 シニア</t>
+        </is>
+      </c>
+      <c r="B26" s="25" t="n">
         <v>104</v>
       </c>
-      <c r="C24" s="25" t="n">
-        <v>124.8</v>
-      </c>
-      <c r="D24" s="19" t="n">
+      <c r="C26" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>参考。Devico/RemoteMore/Wild.Codes 2026（月160h・150円換算）。最も高いため外した</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>シニア級 加重（万円/年）</t>
-        </is>
-      </c>
-      <c r="B26" s="23">
-        <f>SUMPRODUCT(B21:B24,D21:D24)*12</f>
-        <v/>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>参考。最も高い</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>リード級 加重（万円/年）</t>
-        </is>
-      </c>
-      <c r="B27" s="6">
-        <f>SUMPRODUCT(C21:C24,D21:D24)*12</f>
-        <v/>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>AX前提はこちらを使う。人数を減らすかわりに上位層に絞る</t>
-        </is>
+          <t>構成比 合計</t>
+        </is>
+      </c>
+      <c r="C27" s="38">
+        <f>SUM(C21:C26)</f>
+        <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="36" t="inlineStr">
-        <is>
-          <t>⚠ 安い順は ミャンマー(40)＜インド(45)＜フィリピン(47.5)＜ベトナム(50)＜中国(71.7)＜東欧(104)。「中国が安い」のは剪辑師（月18.8万）の話で、エンジニアの受託単価ではない。</t>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>加重単価（万円/年）</t>
+        </is>
+      </c>
+      <c r="B28" s="6">
+        <f>SUMPRODUCT(B21:B26,C21:C26)*12</f>
+        <v/>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>ブリッジSE 20% ＋ プログラマー 80%</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="36" t="inlineStr">
-        <is>
-          <t>⚠ ロシア・ベラルーシは対象外。外為法の役務取引規制（2022/3/18〜）で経産大臣の許可制、限定的な例外を除き許可されない。送金も通らない。単価の問題ではなく、上場審査で主幹事・監査法人が必ず見る論点。ミャンマーは最安だが政情リスクで△。</t>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>⚠ ピラミッドはベトナム内で組む。シニアがミドルをレビューする接点は最もコミュニケーション量が多いので、そこに国・言語・ベンダーの継ぎ目を置かない。社員PMの下が2層で収まる。</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>エンジニアのAX化 — 人数を減らして単価を上げる</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A30" s="36" t="inlineStr">
+        <is>
+          <t>⚠ 安い順は ミャンマー(40)＜インド(45)＜フィリピン(47.5)＜ベトナム(50)＜中国(71.7)＜東欧(104)。ロシア・ベラルーシは外為法の役務取引規制（2022/3/18〜）で対象外。単価の問題ではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>エンジニアのAX化 — 人数を減らして単価の高い層に寄せる</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr"/>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr"/>
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>1期</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>2期</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>3期</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>4期</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>5期</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>考え方</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>必要開発工数（AXなし換算・人年）</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr"/>
-      <c r="C32" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="D32" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" s="18" t="n">
-        <v>20</v>
-      </c>
-      <c r="F32" s="18" t="n">
-        <v>30</v>
-      </c>
-      <c r="G32" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>★プロダクト規模から</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>★ エンジニアのAX倍率</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr"/>
-      <c r="C33" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E33" s="25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F33" s="25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="G33" s="25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>★制作のAX（5期4.0倍）より保守的に置く</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>実エンジニア数（委託）</t>
+          <t>必要開発工数（AXなし換算・人年）</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr"/>
-      <c r="C34" s="23">
-        <f>ROUNDUP(C32/C33,0)</f>
-        <v/>
-      </c>
-      <c r="D34" s="23">
-        <f>ROUNDUP(D32/D33,0)</f>
-        <v/>
-      </c>
-      <c r="E34" s="23">
-        <f>ROUNDUP(E32/E33,0)</f>
-        <v/>
-      </c>
-      <c r="F34" s="23">
-        <f>ROUNDUP(F32/F33,0)</f>
-        <v/>
-      </c>
-      <c r="G34" s="23">
-        <f>ROUNDUP(G32/G33,0)</f>
-        <v/>
+      <c r="C34" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F34" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="G34" s="18" t="n">
+        <v>40</v>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>必要工数 ÷ AX倍率</t>
+          <t>★プロダクト規模から</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
+          <t>★ エンジニアのAX倍率</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr"/>
+      <c r="C35" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E35" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F35" s="25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G35" s="25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>★ミドル中心なのでレビューがボトルネックになる。制作(4.0)より低く置く</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>実エンジニア数（委託）</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr"/>
+      <c r="C36" s="23">
+        <f>ROUNDUP(C34/C35,0)</f>
+        <v/>
+      </c>
+      <c r="D36" s="23">
+        <f>ROUNDUP(D34/D35,0)</f>
+        <v/>
+      </c>
+      <c r="E36" s="23">
+        <f>ROUNDUP(E34/E35,0)</f>
+        <v/>
+      </c>
+      <c r="F36" s="23">
+        <f>ROUNDUP(F34/F35,0)</f>
+        <v/>
+      </c>
+      <c r="G36" s="23">
+        <f>ROUNDUP(G34/G35,0)</f>
+        <v/>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>必要工数 ÷ AX倍率</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
           <t>PM（社員）</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr"/>
-      <c r="C35" s="23">
-        <f>ROUNDUP(C34/5,0)</f>
-        <v/>
-      </c>
-      <c r="D35" s="23">
-        <f>ROUNDUP(D34/5,0)</f>
-        <v/>
-      </c>
-      <c r="E35" s="23">
-        <f>ROUNDUP(E34/5,0)</f>
-        <v/>
-      </c>
-      <c r="F35" s="23">
-        <f>ROUNDUP(F34/5,0)</f>
-        <v/>
-      </c>
-      <c r="G35" s="23">
-        <f>ROUNDUP(G34/5,0)</f>
-        <v/>
-      </c>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr"/>
+      <c r="C37" s="23">
+        <f>ROUNDUP(C36/5,0)</f>
+        <v/>
+      </c>
+      <c r="D37" s="23">
+        <f>ROUNDUP(D36/5,0)</f>
+        <v/>
+      </c>
+      <c r="E37" s="23">
+        <f>ROUNDUP(E36/5,0)</f>
+        <v/>
+      </c>
+      <c r="F37" s="23">
+        <f>ROUNDUP(F36/5,0)</f>
+        <v/>
+      </c>
+      <c r="G37" s="23">
+        <f>ROUNDUP(G36/5,0)</f>
+        <v/>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>1名で5名を見る。上の人件費表はここを参照</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>開発委託費（百万円）</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr"/>
-      <c r="C36" s="6">
-        <f>C34*$B$27/100</f>
-        <v/>
-      </c>
-      <c r="D36" s="6">
-        <f>D34*$B$27/100</f>
-        <v/>
-      </c>
-      <c r="E36" s="6">
-        <f>E34*$B$27/100</f>
-        <v/>
-      </c>
-      <c r="F36" s="6">
-        <f>F34*$B$27/100</f>
-        <v/>
-      </c>
-      <c r="G36" s="6">
-        <f>G34*$B$27/100</f>
-        <v/>
-      </c>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>実人数 × リード級の年額</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>旧構成は社員40名。PM4名＋委託16名になる。単価は年808万→926万に上げても、委託費は5期300→148百万。1〜2期は逆に高くつく（AX倍率が立つ前に単価だけ上がるため）。制作のAXと同じ形で、先に投資して後で効く。</t>
+      <c r="B38" s="5" t="inlineStr"/>
+      <c r="C38" s="6">
+        <f>C36*$B$28/100</f>
+        <v/>
+      </c>
+      <c r="D38" s="6">
+        <f>D36*$B$28/100</f>
+        <v/>
+      </c>
+      <c r="E38" s="6">
+        <f>E36*$B$28/100</f>
+        <v/>
+      </c>
+      <c r="F38" s="6">
+        <f>F36*$B$28/100</f>
+        <v/>
+      </c>
+      <c r="G38" s="6">
+        <f>G36*$B$28/100</f>
+        <v/>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>実人数 × 加重単価</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="12" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>旧構成は社員40名。PM4名＋委託19名になる。加重単価は年527万で、中国シニア20%＋ベトナムミドル80%（557万）より安く、継ぎ目もない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="36" t="inlineStr">
+        <is>
+          <t>⚠ 管理・コーポレート3名は、5期に上場会社として内部統制報告制度の対象になる規模には薄い。取引処理はBPOに出す前提だが、内部統制の設計・運用・評価は社員の仕事。監査法人と主幹事に早期に当てること。★確認事項</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>社外の専門家を前提にするなら、その費用が見えている必要がある</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>管理3名で回るのは顧問弁護士・監査法人・社労士が外にいるから。その費用は「その他販管費（売上の4%）」に入っている。5期で足りるかの検算。</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>費目</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>下限</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>上限</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr"/>
-      <c r="E42" s="3" t="inlineStr"/>
-      <c r="F42" s="3" t="inlineStr"/>
-      <c r="G42" s="3" t="inlineStr"/>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>監査報酬（上場後）</t>
-        </is>
-      </c>
-      <c r="B43" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="C43" s="18" t="n">
-        <v>70</v>
-      </c>
-      <c r="H43" s="7" t="inlineStr">
-        <is>
-          <t>上場会社・売上108億規模</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>株式事務代行・IR</t>
-        </is>
-      </c>
-      <c r="B44" s="18" t="n">
-        <v>20</v>
-      </c>
-      <c r="C44" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="H44" s="7" t="inlineStr">
-        <is>
-          <t>信託銀行・開示書類・説明会</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>顧問弁護士</t>
-        </is>
-      </c>
-      <c r="B45" s="18" t="n">
-        <v>12</v>
-      </c>
-      <c r="C45" s="18" t="n">
-        <v>30</v>
-      </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>契約審査・中国パートナー・業務委託設計</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>税理士・社会保険労務士</t>
+          <t>監査報酬（上場後）</t>
         </is>
       </c>
       <c r="B46" s="18" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="C46" s="18" t="n">
-        <v>12</v>
-      </c>
-      <c r="H46" s="7" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>上場会社・売上108億規模</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>オフィス（社員26名）</t>
+          <t>株式事務代行・IR</t>
         </is>
       </c>
       <c r="B47" s="18" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C47" s="18" t="n">
-        <v>50</v>
-      </c>
-      <c r="H47" s="7" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>信託銀行・開示書類・説明会</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>SaaS・通信・インフラ（非開発）</t>
+          <t>顧問弁護士</t>
         </is>
       </c>
       <c r="B48" s="18" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C48" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="H48" s="7" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>契約審査・中国パートナー・業務委託設計</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>採用・教育</t>
+          <t>税理士・社会保険労務士</t>
         </is>
       </c>
       <c r="B49" s="18" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C49" s="18" t="n">
-        <v>60</v>
-      </c>
-      <c r="H49" s="7" t="inlineStr">
-        <is>
-          <t>PM・統括級の採用は単価が高い</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H49" s="7" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>旅費交通</t>
+          <t>オフィス（社員22名）</t>
         </is>
       </c>
       <c r="B50" s="18" t="n">
         <v>30</v>
       </c>
       <c r="C50" s="18" t="n">
-        <v>60</v>
-      </c>
-      <c r="H50" s="7" t="inlineStr">
-        <is>
-          <t>中国・ベトナム・東欧の往復</t>
-        </is>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="H50" s="7" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>保険・その他</t>
+          <t>SaaS・通信・インフラ（非開発）</t>
         </is>
       </c>
       <c r="B51" s="18" t="n">
@@ -12697,32 +12674,92 @@
       <c r="H51" s="7" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="B52" s="21">
-        <f>SUM(B43:B51)</f>
-        <v/>
-      </c>
-      <c r="C52" s="21">
-        <f>SUM(C43:C51)</f>
-        <v/>
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>採用・教育</t>
+        </is>
+      </c>
+      <c r="B52" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="C52" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>PM・統括級の採用は単価が高い</t>
+        </is>
       </c>
     </row>
     <row r="53">
-      <c r="C53" s="6">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>旅費交通</t>
+        </is>
+      </c>
+      <c r="B53" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="C53" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>ベトナム・インド往復</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>保険・その他</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="C54" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="H54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>合計（百万円）</t>
+        </is>
+      </c>
+      <c r="B55" s="21">
+        <f>SUM(B46:B54)</f>
+        <v/>
+      </c>
+      <c r="C55" s="21">
+        <f>SUM(C46:C54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>その他販管費（5期・売上の4%）</t>
+        </is>
+      </c>
+      <c r="C56" s="6">
         <f>'損益計算書'!G27</f>
         <v/>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
-      <c r="C54" s="34">
-        <f>IF(C53&gt;=C52,"○ 上限まで賄える","× 足りない")</f>
-        <v/>
-      </c>
-      <c r="H54" s="7" t="inlineStr">
+      <c r="C57" s="34">
+        <f>IF(C56&gt;=C55,"○ 上限まで賄える","× 足りない")</f>
+        <v/>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
         <is>
           <t>★費目はすべて私の見積もり。実際の見積を取ったものではない</t>
         </is>
